--- a/database/event/3427/event_3427_evp_summary.xlsx
+++ b/database/event/3427/event_3427_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.8628</v>
+        <v>5.4279</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4883</v>
+        <v>0.545</v>
       </c>
       <c r="D2" t="n">
-        <v>1.5431</v>
+        <v>1.7186</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8628</v>
+        <v>5.4279</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3905</v>
+        <v>1.9556</v>
       </c>
       <c r="G2" t="n">
         <v>3.4723</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3905</v>
+        <v>1.9556</v>
       </c>
       <c r="I2" t="n">
-        <v>1.127</v>
+        <v>1.5851</v>
       </c>
       <c r="J2" t="n">
         <v>3.4723</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5993</v>
+        <v>5.0574</v>
       </c>
       <c r="N2" t="n">
         <v>152</v>
@@ -538,265 +538,265 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>nexa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.6171</v>
+        <v>5.2212</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4636</v>
+        <v>0.5243</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4438</v>
+        <v>1.6362</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6171</v>
+        <v>5.2212</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7314</v>
+        <v>3.2566</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8857</v>
+        <v>1.9646</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7314</v>
+        <v>3.2566</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0244</v>
+        <v>2.6396</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8857</v>
+        <v>1.9646</v>
       </c>
       <c r="K3" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="L3" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9101</v>
+        <v>4.604200000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>nexa</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6095</v>
+        <v>4.6171</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4629</v>
+        <v>0.4636</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4408</v>
+        <v>1.3955</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6095</v>
+        <v>4.6171</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6449</v>
+        <v>3.7314</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9646</v>
+        <v>0.8857</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6449</v>
+        <v>3.7314</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1438</v>
+        <v>3.0244</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9646</v>
+        <v>0.8857</v>
       </c>
       <c r="K4" t="n">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="L4" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1084</v>
+        <v>3.9101</v>
       </c>
       <c r="N4" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1373</v>
+        <v>4.3733</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4154</v>
+        <v>0.4391</v>
       </c>
       <c r="D5" t="n">
-        <v>1.25</v>
+        <v>1.2984</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1373</v>
+        <v>4.3733</v>
       </c>
       <c r="F5" t="n">
-        <v>3.1268</v>
+        <v>3.3944</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0105</v>
+        <v>0.9789</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1268</v>
+        <v>3.3944</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5344</v>
+        <v>2.7512</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0105</v>
+        <v>0.9789</v>
       </c>
       <c r="K5" t="n">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="L5" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M5" t="n">
-        <v>3.5449</v>
+        <v>3.7301</v>
       </c>
       <c r="N5" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9547</v>
+        <v>4.1373</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3971</v>
+        <v>0.4154</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1762</v>
+        <v>1.2044</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9547</v>
+        <v>4.1373</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2021</v>
+        <v>3.1268</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2474</v>
+        <v>1.0105</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3453</v>
+        <v>3.1268</v>
       </c>
       <c r="I6" t="n">
-        <v>3.522</v>
+        <v>2.5344</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2474</v>
+        <v>1.0105</v>
       </c>
       <c r="K6" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L6" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2746</v>
+        <v>3.5449</v>
       </c>
       <c r="N6" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7979</v>
+        <v>3.9547</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3814</v>
+        <v>0.3971</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1129</v>
+        <v>1.1316</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7979</v>
+        <v>3.9547</v>
       </c>
       <c r="F7" t="n">
-        <v>3.631</v>
+        <v>4.2021</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1669</v>
+        <v>-0.2474</v>
       </c>
       <c r="H7" t="n">
-        <v>3.631</v>
+        <v>4.3453</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9431</v>
+        <v>3.522</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1669</v>
+        <v>-0.2474</v>
       </c>
       <c r="K7" t="n">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="L7" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>3.11</v>
+        <v>3.2746</v>
       </c>
       <c r="N7" t="n">
-        <v>298</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7876</v>
+        <v>3.7979</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3803</v>
+        <v>0.3814</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1087</v>
+        <v>1.0692</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7876</v>
+        <v>3.7979</v>
       </c>
       <c r="F8" t="n">
-        <v>2.777</v>
+        <v>3.631</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0106</v>
+        <v>0.1669</v>
       </c>
       <c r="H8" t="n">
-        <v>2.777</v>
+        <v>3.631</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2509</v>
+        <v>2.9431</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0106</v>
+        <v>0.1669</v>
       </c>
       <c r="K8" t="n">
         <v>202</v>
@@ -805,7 +805,7 @@
         <v>96</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2615</v>
+        <v>3.11</v>
       </c>
       <c r="N8" t="n">
         <v>298</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6951</v>
+        <v>3.7876</v>
       </c>
       <c r="C9" t="n">
-        <v>0.371</v>
+        <v>0.3803</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0714</v>
+        <v>1.0651</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6951</v>
+        <v>3.7876</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7162</v>
+        <v>2.777</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9789</v>
+        <v>1.0106</v>
       </c>
       <c r="H9" t="n">
-        <v>2.7162</v>
+        <v>2.777</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2016</v>
+        <v>2.2509</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9789</v>
+        <v>1.0106</v>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="L9" t="n">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1805</v>
+        <v>3.2615</v>
       </c>
       <c r="N9" t="n">
-        <v>191</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5896</v>
+        <v>3.6627</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3604</v>
+        <v>0.3678</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0288</v>
+        <v>1.0153</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5896</v>
+        <v>3.6627</v>
       </c>
       <c r="F10" t="n">
-        <v>1.402</v>
+        <v>1.4751</v>
       </c>
       <c r="G10" t="n">
         <v>2.1876</v>
       </c>
       <c r="H10" t="n">
-        <v>1.402</v>
+        <v>1.4751</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1364</v>
+        <v>1.1956</v>
       </c>
       <c r="J10" t="n">
         <v>2.1876</v>
@@ -897,7 +897,7 @@
         <v>104</v>
       </c>
       <c r="M10" t="n">
-        <v>3.324</v>
+        <v>3.3832</v>
       </c>
       <c r="N10" t="n">
         <v>152</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.0337</v>
+        <v>3.4774</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3046</v>
+        <v>0.3492</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8042</v>
+        <v>0.9415</v>
       </c>
       <c r="E11" t="n">
-        <v>3.0337</v>
+        <v>3.4774</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6656</v>
+        <v>2.3437</v>
       </c>
       <c r="G11" t="n">
-        <v>1.3681</v>
+        <v>1.1337</v>
       </c>
       <c r="H11" t="n">
-        <v>1.6656</v>
+        <v>2.3437</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3501</v>
+        <v>1.8997</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3681</v>
+        <v>1.1337</v>
       </c>
       <c r="K11" t="n">
         <v>44</v>
@@ -943,7 +943,7 @@
         <v>147</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7182</v>
+        <v>3.0334</v>
       </c>
       <c r="N11" t="n">
         <v>191</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9172</v>
+        <v>3.1081</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2929</v>
+        <v>0.3121</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7571</v>
+        <v>0.7944</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9172</v>
+        <v>3.1081</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7835</v>
+        <v>1.74</v>
       </c>
       <c r="G12" t="n">
-        <v>1.1337</v>
+        <v>1.3681</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7835</v>
+        <v>1.74</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4455</v>
+        <v>1.4103</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1337</v>
+        <v>1.3681</v>
       </c>
       <c r="K12" t="n">
         <v>44</v>
@@ -989,7 +989,7 @@
         <v>147</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5792</v>
+        <v>2.7784</v>
       </c>
       <c r="N12" t="n">
         <v>191</v>
@@ -998,139 +998,139 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>gade</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6516</v>
+        <v>1.7387</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1658</v>
+        <v>0.1746</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2458</v>
+        <v>0.2488</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6516</v>
+        <v>1.7387</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6516</v>
+        <v>1.8988</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.1601</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6516</v>
+        <v>1.8988</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6516</v>
+        <v>1.539</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.1601</v>
       </c>
       <c r="K13" t="n">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6516</v>
+        <v>1.3789</v>
       </c>
       <c r="N13" t="n">
-        <v>119</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gade</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5753</v>
+        <v>1.7068</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1582</v>
+        <v>0.1714</v>
       </c>
       <c r="D14" t="n">
-        <v>0.215</v>
+        <v>0.2361</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5753</v>
+        <v>1.7068</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7354</v>
+        <v>1.7068</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1601</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7354</v>
+        <v>1.7068</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4066</v>
+        <v>1.7068</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1601</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2465</v>
+        <v>1.7068</v>
       </c>
       <c r="N14" t="n">
-        <v>191</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1453</v>
+        <v>0.1658</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1632</v>
+        <v>0.2141</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4469</v>
+        <v>1.6516</v>
       </c>
       <c r="N15" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16">
@@ -1146,7 +1146,7 @@
         <v>0.1326</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1121</v>
+        <v>0.0822</v>
       </c>
       <c r="E16" t="n">
         <v>1.3206</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1195</v>
+        <v>0.1283</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0593</v>
+        <v>0.065</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1897</v>
+        <v>1.2774</v>
       </c>
       <c r="N17" t="n">
         <v>159</v>
@@ -1238,7 +1238,7 @@
         <v>0.0604</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1783</v>
+        <v>-0.2042</v>
       </c>
       <c r="E18" t="n">
         <v>0.6016</v>
@@ -1274,492 +1274,492 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0341</v>
+        <v>0.0505</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2842</v>
+        <v>-0.2434</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3395</v>
+        <v>0.5033</v>
       </c>
       <c r="N19" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2487</v>
+        <v>0.3395</v>
       </c>
       <c r="C20" t="n">
-        <v>0.025</v>
+        <v>0.0341</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3209</v>
+        <v>-0.3087</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2487</v>
+        <v>0.3395</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7008</v>
+        <v>0.3395</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4521</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7008</v>
+        <v>0.3395</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.3395</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4521</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L20" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1158999999999999</v>
+        <v>0.3395</v>
       </c>
       <c r="N20" t="n">
-        <v>182</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1904</v>
+        <v>0.2487</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0191</v>
+        <v>0.025</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3444</v>
+        <v>-0.3448</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1904</v>
+        <v>0.2487</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1904</v>
+        <v>0.7008</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.4521</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1904</v>
+        <v>0.7008</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1904</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.4521</v>
       </c>
       <c r="K21" t="n">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1904</v>
+        <v>0.1158999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>72</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0133</v>
+        <v>0.0191</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.368</v>
+        <v>-0.3681</v>
       </c>
       <c r="E22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="F22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="I22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.132</v>
+        <v>0.1904</v>
       </c>
       <c r="N22" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1111</v>
+        <v>0.132</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0112</v>
+        <v>0.0133</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3765</v>
+        <v>-0.3913</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1111</v>
+        <v>0.132</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1111</v>
+        <v>0.132</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1111</v>
+        <v>0.132</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9006</v>
+        <v>0.132</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>202</v>
+        <v>119</v>
       </c>
       <c r="L23" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.09940000000000004</v>
+        <v>0.132</v>
       </c>
       <c r="N23" t="n">
-        <v>298</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1111</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0067</v>
+        <v>0.0112</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3945</v>
+        <v>-0.3996</v>
       </c>
       <c r="E24" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.1111</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8499</v>
+        <v>1.1111</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.7833</v>
+        <v>-1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8499</v>
+        <v>1.1111</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6889</v>
+        <v>0.9006</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7833</v>
+        <v>-1</v>
       </c>
       <c r="K24" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L24" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.09440000000000004</v>
+        <v>-0.09940000000000004</v>
       </c>
       <c r="N24" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.0052</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0005</v>
+        <v>0.0067</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4235</v>
+        <v>-0.4174</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.0052</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0052</v>
+        <v>0.8499</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.7833</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0052</v>
+        <v>0.8499</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0052</v>
+        <v>0.6889</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.7833</v>
       </c>
       <c r="K25" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0052</v>
+        <v>-0.09440000000000004</v>
       </c>
       <c r="N25" t="n">
-        <v>97</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0015</v>
+        <v>-0.0005</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4274</v>
+        <v>-0.4459</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>159</v>
+        <v>97</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.015</v>
+        <v>-0.005</v>
       </c>
       <c r="N26" t="n">
-        <v>159</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0311</v>
+        <v>-0.0015</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5466</v>
+        <v>-0.4499</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.31</v>
+        <v>-0.015</v>
       </c>
       <c r="N27" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0321</v>
+        <v>-0.0311</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5504</v>
+        <v>-0.5674</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3195</v>
+        <v>-0.31</v>
       </c>
       <c r="N28" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0348</v>
+        <v>-0.0321</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5614</v>
+        <v>-0.5712</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3466</v>
+        <v>-0.3195</v>
       </c>
       <c r="N29" t="n">
         <v>97</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0612</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6674</v>
+        <v>-0.6866</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6091</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0718</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7104</v>
+        <v>-0.7289</v>
       </c>
       <c r="E31" t="n">
         <v>-0.7154</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0789</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7389</v>
+        <v>-0.7571</v>
       </c>
       <c r="E32" t="n">
         <v>-0.786</v>
@@ -1928,7 +1928,7 @@
         <v>-0.0866</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7696</v>
+        <v>-0.7873</v>
       </c>
       <c r="E33" t="n">
         <v>-0.862</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0983</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8167</v>
+        <v>-0.8338</v>
       </c>
       <c r="E34" t="n">
         <v>-0.9786</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0988</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8189</v>
+        <v>-0.8359</v>
       </c>
       <c r="E35" t="n">
         <v>-0.984</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1099</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8635</v>
+        <v>-0.88</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0945</v>
@@ -2112,7 +2112,7 @@
         <v>-0.11</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8639</v>
+        <v>-0.8804</v>
       </c>
       <c r="E37" t="n">
         <v>-1.0955</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1207</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9069</v>
+        <v>-0.9227</v>
       </c>
       <c r="E38" t="n">
         <v>-1.2019</v>
@@ -2204,7 +2204,7 @@
         <v>-0.1371</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9729</v>
+        <v>-0.9878</v>
       </c>
       <c r="E39" t="n">
         <v>-1.3653</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2689</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5033</v>
+        <v>-1.5109</v>
       </c>
       <c r="E40" t="n">
         <v>-2.6781</v>
@@ -2296,7 +2296,7 @@
         <v>-0.3016</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6348</v>
+        <v>-1.6406</v>
       </c>
       <c r="E41" t="n">
         <v>-3.0037</v>

--- a/database/event/3427/event_3427_evp_summary.xlsx
+++ b/database/event/3427/event_3427_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4279</v>
+        <v>5.3674</v>
       </c>
       <c r="C2" t="n">
-        <v>0.545</v>
+        <v>0.539</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7186</v>
+        <v>1.7851</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4279</v>
+        <v>5.3674</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9556</v>
+        <v>2.3287</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4723</v>
+        <v>3.0387</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9556</v>
+        <v>2.7187</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5851</v>
+        <v>1.4136</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4723</v>
+        <v>3.0387</v>
       </c>
       <c r="K2" t="n">
         <v>48</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>5.0574</v>
+        <v>4.4523</v>
       </c>
       <c r="N2" t="n">
         <v>152</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2212</v>
+        <v>4.8846</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5243</v>
+        <v>0.4905</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6362</v>
+        <v>1.5671</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2212</v>
+        <v>4.8846</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2566</v>
+        <v>2.8617</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9646</v>
+        <v>2.0229</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2566</v>
+        <v>4.5967</v>
       </c>
       <c r="I3" t="n">
-        <v>2.6396</v>
+        <v>2.3901</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9646</v>
+        <v>2.0229</v>
       </c>
       <c r="K3" t="n">
         <v>48</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>4.604200000000001</v>
+        <v>4.413</v>
       </c>
       <c r="N3" t="n">
         <v>152</v>
@@ -584,127 +584,127 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HObbit</t>
+          <t>nukkye</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.6171</v>
+        <v>4.3444</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4636</v>
+        <v>0.4362</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3955</v>
+        <v>1.3233</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6171</v>
+        <v>4.3444</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7314</v>
+        <v>2.2537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8857</v>
+        <v>2.0907</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7314</v>
+        <v>2.4544</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0244</v>
+        <v>1.2762</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8857</v>
+        <v>2.0907</v>
       </c>
       <c r="K4" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="L4" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9101</v>
+        <v>3.3669</v>
       </c>
       <c r="N4" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>HObbit</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3733</v>
+        <v>4.1603</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4391</v>
+        <v>0.4178</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2984</v>
+        <v>1.2402</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3733</v>
+        <v>4.1603</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3944</v>
+        <v>3.3008</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9789</v>
+        <v>0.8595</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3944</v>
+        <v>6.1436</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7512</v>
+        <v>3.1944</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9789</v>
+        <v>0.8595</v>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="L5" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7301</v>
+        <v>4.0539</v>
       </c>
       <c r="N5" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1373</v>
+        <v>4.1098</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4154</v>
+        <v>0.4127</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2044</v>
+        <v>1.2174</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1373</v>
+        <v>4.1098</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1268</v>
+        <v>3.1642</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0105</v>
+        <v>0.9456</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1268</v>
+        <v>5.6624</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5344</v>
+        <v>2.9442</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0105</v>
+        <v>0.9456</v>
       </c>
       <c r="K6" t="n">
         <v>202</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5449</v>
+        <v>3.8898</v>
       </c>
       <c r="N6" t="n">
         <v>298</v>
@@ -722,265 +722,265 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.9547</v>
+        <v>4.0846</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3971</v>
+        <v>0.4101</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1316</v>
+        <v>1.206</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9547</v>
+        <v>4.0846</v>
       </c>
       <c r="F7" t="n">
-        <v>4.2021</v>
+        <v>3.2714</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2474</v>
+        <v>0.8132</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3453</v>
+        <v>6.04</v>
       </c>
       <c r="I7" t="n">
-        <v>3.522</v>
+        <v>3.1405</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2474</v>
+        <v>0.8132</v>
       </c>
       <c r="K7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L7" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2746</v>
+        <v>3.9537</v>
       </c>
       <c r="N7" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.7979</v>
+        <v>3.9383</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3814</v>
+        <v>0.3955</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0692</v>
+        <v>1.1399</v>
       </c>
       <c r="E8" t="n">
-        <v>3.7979</v>
+        <v>3.9383</v>
       </c>
       <c r="F8" t="n">
-        <v>3.631</v>
+        <v>2.9425</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1669</v>
+        <v>0.9958</v>
       </c>
       <c r="H8" t="n">
-        <v>3.631</v>
+        <v>4.8814</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9431</v>
+        <v>2.5381</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1669</v>
+        <v>0.9958</v>
       </c>
       <c r="K8" t="n">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="L8" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>3.11</v>
+        <v>3.5339</v>
       </c>
       <c r="N8" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7876</v>
+        <v>3.655</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3803</v>
+        <v>0.367</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0651</v>
+        <v>1.012</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7876</v>
+        <v>3.655</v>
       </c>
       <c r="F9" t="n">
-        <v>2.777</v>
+        <v>2.3943</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0106</v>
+        <v>1.2607</v>
       </c>
       <c r="H9" t="n">
-        <v>2.777</v>
+        <v>2.9499</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2509</v>
+        <v>1.5338</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0106</v>
+        <v>1.2607</v>
       </c>
       <c r="K9" t="n">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="L9" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2615</v>
+        <v>2.7945</v>
       </c>
       <c r="N9" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nukkye</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6627</v>
+        <v>3.6175</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3678</v>
+        <v>0.3632</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0153</v>
+        <v>0.9951</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6627</v>
+        <v>3.6175</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4751</v>
+        <v>3.707</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1876</v>
+        <v>-0.0895</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4751</v>
+        <v>7.5747</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1956</v>
+        <v>3.9385</v>
       </c>
       <c r="J10" t="n">
-        <v>2.1876</v>
+        <v>-0.0895</v>
       </c>
       <c r="K10" t="n">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="L10" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3832</v>
+        <v>3.849</v>
       </c>
       <c r="N10" t="n">
-        <v>152</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4774</v>
+        <v>3.6084</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3492</v>
+        <v>0.3623</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9415</v>
+        <v>0.991</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4774</v>
+        <v>3.6084</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3437</v>
+        <v>3.3584</v>
       </c>
       <c r="G11" t="n">
-        <v>1.1337</v>
+        <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3437</v>
+        <v>6.3467</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8997</v>
+        <v>3.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1337</v>
+        <v>0.25</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="L11" t="n">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.0334</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>191</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.1081</v>
+        <v>3.5092</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3121</v>
+        <v>0.3524</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7944</v>
+        <v>0.9462</v>
       </c>
       <c r="E12" t="n">
-        <v>3.1081</v>
+        <v>3.5092</v>
       </c>
       <c r="F12" t="n">
-        <v>1.74</v>
+        <v>2.5104</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3681</v>
+        <v>0.9988</v>
       </c>
       <c r="H12" t="n">
-        <v>1.74</v>
+        <v>3.3586</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4103</v>
+        <v>1.7463</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3681</v>
+        <v>0.9988</v>
       </c>
       <c r="K12" t="n">
         <v>44</v>
@@ -989,7 +989,7 @@
         <v>147</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7784</v>
+        <v>2.7451</v>
       </c>
       <c r="N12" t="n">
         <v>191</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7387</v>
+        <v>2.5775</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1746</v>
+        <v>0.2588</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2488</v>
+        <v>0.5256</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7387</v>
+        <v>2.5775</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8988</v>
+        <v>2.4534</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1601</v>
+        <v>0.1241</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8988</v>
+        <v>3.158</v>
       </c>
       <c r="I13" t="n">
-        <v>1.539</v>
+        <v>1.642</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.1601</v>
+        <v>0.1241</v>
       </c>
       <c r="K13" t="n">
         <v>44</v>
@@ -1035,7 +1035,7 @@
         <v>147</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3789</v>
+        <v>1.7661</v>
       </c>
       <c r="N13" t="n">
         <v>191</v>
@@ -1044,599 +1044,599 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>AdreN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7068</v>
+        <v>2.2188</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1714</v>
+        <v>0.2228</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2361</v>
+        <v>0.3637</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7068</v>
+        <v>2.2188</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7068</v>
+        <v>2.3869</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0.1681</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7068</v>
+        <v>2.9235</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7068</v>
+        <v>1.5201</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0.1681</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7068</v>
+        <v>1.352</v>
       </c>
       <c r="N14" t="n">
-        <v>97</v>
+        <v>182</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>hampus</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1658</v>
+        <v>0.1936</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2141</v>
+        <v>0.2322</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6516</v>
+        <v>1.9277</v>
       </c>
       <c r="N15" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AdreN</t>
+          <t>hampus</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3206</v>
+        <v>1.8063</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1326</v>
+        <v>0.1814</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0822</v>
+        <v>0.1774</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3206</v>
+        <v>1.8063</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6708</v>
+        <v>1.8063</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3502</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6708</v>
+        <v>1.8063</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3542</v>
+        <v>1.8063</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3502</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="L16" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.004</v>
+        <v>1.8063</v>
       </c>
       <c r="N16" t="n">
-        <v>182</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2774</v>
+        <v>1.6801</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1283</v>
+        <v>0.1687</v>
       </c>
       <c r="D17" t="n">
-        <v>0.065</v>
+        <v>0.1205</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2774</v>
+        <v>1.6801</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2774</v>
+        <v>2.177</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.4969</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2774</v>
+        <v>2.184</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2774</v>
+        <v>1.1356</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4969</v>
       </c>
       <c r="K17" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2774</v>
+        <v>0.6386999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>kRYSTAL</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6016</v>
+        <v>1.5861</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0604</v>
+        <v>0.1593</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2042</v>
+        <v>0.078</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6016</v>
+        <v>1.5861</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4223</v>
+        <v>2.2421</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1793</v>
+        <v>-0.656</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4223</v>
+        <v>2.4135</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3423</v>
+        <v>1.2549</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1793</v>
+        <v>-0.656</v>
       </c>
       <c r="K18" t="n">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="L18" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5216</v>
+        <v>0.5988999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>152</v>
+        <v>298</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0505</v>
+        <v>0.1435</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2434</v>
+        <v>0.0073</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5033</v>
+        <v>1.4295</v>
       </c>
       <c r="N19" t="n">
-        <v>97</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>jkaem</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3395</v>
+        <v>1.3784</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0341</v>
+        <v>0.1384</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3087</v>
+        <v>-0.0157</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3395</v>
+        <v>1.3784</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3395</v>
+        <v>1.66</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2816</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3395</v>
+        <v>1.66</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3395</v>
+        <v>0.8631</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2816</v>
       </c>
       <c r="K20" t="n">
-        <v>72</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3395</v>
+        <v>0.5814999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>72</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>kRYSTAL</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2487</v>
+        <v>1.1021</v>
       </c>
       <c r="C21" t="n">
-        <v>0.025</v>
+        <v>0.1107</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3448</v>
+        <v>-0.1405</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2487</v>
+        <v>1.1021</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7008</v>
+        <v>0.8726</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4521</v>
+        <v>0.2295</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7008</v>
+        <v>0.8726</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.4537</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4521</v>
+        <v>0.2295</v>
       </c>
       <c r="K21" t="n">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="L21" t="n">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1158999999999999</v>
+        <v>0.6832</v>
       </c>
       <c r="N21" t="n">
-        <v>182</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jks</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0191</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3681</v>
+        <v>-0.3232</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1904</v>
+        <v>0.6973</v>
       </c>
       <c r="N22" t="n">
-        <v>72</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brollan</t>
+          <t>jkaem</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0133</v>
+        <v>0.0465</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3913</v>
+        <v>-0.4289</v>
       </c>
       <c r="E23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="F23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="I23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.132</v>
+        <v>0.4633</v>
       </c>
       <c r="N23" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1111</v>
+        <v>0.4214</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0112</v>
+        <v>0.0423</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3996</v>
+        <v>-0.4478</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1111</v>
+        <v>0.4214</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1111</v>
+        <v>0.4214</v>
       </c>
       <c r="G24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1111</v>
+        <v>0.4214</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9006</v>
+        <v>0.4214</v>
       </c>
       <c r="J24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>202</v>
+        <v>97</v>
       </c>
       <c r="L24" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.09940000000000004</v>
+        <v>0.4214</v>
       </c>
       <c r="N24" t="n">
-        <v>298</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>jks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.4078</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0067</v>
+        <v>0.0409</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4174</v>
+        <v>-0.4539</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.4078</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8499</v>
+        <v>0.4078</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7833</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8499</v>
+        <v>0.4078</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6889</v>
+        <v>0.4078</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7833</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>129</v>
+        <v>72</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.09440000000000004</v>
+        <v>0.4078</v>
       </c>
       <c r="N25" t="n">
-        <v>182</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>Brollan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0005</v>
+        <v>0.0286</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4459</v>
+        <v>-0.5095</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.005</v>
+        <v>0.2846</v>
       </c>
       <c r="N26" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0015</v>
+        <v>0.0202</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4499</v>
+        <v>-0.547</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.015</v>
+        <v>0.2015</v>
       </c>
       <c r="N27" t="n">
         <v>159</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0311</v>
+        <v>0.0142</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5674</v>
+        <v>-0.5743</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.31</v>
+        <v>0.1411</v>
       </c>
       <c r="N28" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0321</v>
+        <v>0.0004</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5712</v>
+        <v>-0.6364</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3195</v>
+        <v>0.0036</v>
       </c>
       <c r="N29" t="n">
         <v>97</v>
@@ -1780,78 +1780,78 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0612</v>
+        <v>-0.0007</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6866</v>
+        <v>-0.6412</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.6091</v>
+        <v>-0.0071</v>
       </c>
       <c r="N30" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TOAO</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0718</v>
+        <v>-0.0447</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7289</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7154</v>
+        <v>-0.4456</v>
       </c>
       <c r="N31" t="n">
         <v>159</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0789</v>
+        <v>-0.046</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7571</v>
+        <v>-0.8446</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.786</v>
+        <v>-0.4577</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1918,32 +1918,32 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>TOAO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0866</v>
+        <v>-0.0512</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7873</v>
+        <v>-0.868</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.862</v>
+        <v>-0.5095</v>
       </c>
       <c r="N33" t="n">
         <v>159</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0983</v>
+        <v>-0.0688</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8338</v>
+        <v>-0.9475</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9786</v>
+        <v>-0.6855</v>
       </c>
       <c r="N34" t="n">
         <v>159</v>
@@ -2010,170 +2010,170 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>twist</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0988</v>
+        <v>-0.0743</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8359</v>
+        <v>-0.9722</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.984</v>
+        <v>-0.7402</v>
       </c>
       <c r="N35" t="n">
-        <v>119</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>twist</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1099</v>
+        <v>-0.0796</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.88</v>
+        <v>-0.9957</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0945</v>
+        <v>-0.7924</v>
       </c>
       <c r="N36" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TENZKI</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0955</v>
+        <v>-0.8022</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.11</v>
+        <v>-0.0806</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8804</v>
+        <v>-1.0002</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0955</v>
+        <v>-0.8022</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0773</v>
+        <v>-0.8022</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.0182</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0773</v>
+        <v>-0.8022</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8732</v>
+        <v>-0.8022</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.0182</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L37" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8914</v>
+        <v>-0.8022</v>
       </c>
       <c r="N37" t="n">
-        <v>152</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1207</v>
+        <v>-0.09</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9227</v>
+        <v>-1.0425</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.2019</v>
+        <v>-0.896</v>
       </c>
       <c r="N38" t="n">
         <v>72</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>TENZKI</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3653</v>
+        <v>-1.3621</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1371</v>
+        <v>-0.1368</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9878</v>
+        <v>-1.2529</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3653</v>
+        <v>-1.3621</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.3653</v>
+        <v>-1.4303</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.3653</v>
+        <v>-1.4303</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.3653</v>
+        <v>-0.7437</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.0682</v>
       </c>
       <c r="K39" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.3653</v>
+        <v>-0.6755</v>
       </c>
       <c r="N39" t="n">
-        <v>72</v>
+        <v>152</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6781</v>
+        <v>-2.6093</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2689</v>
+        <v>-0.262</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5109</v>
+        <v>-1.816</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6781</v>
+        <v>-2.6093</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.4674</v>
+        <v>-2.5302</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.2107</v>
+        <v>-0.0791</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.4674</v>
+        <v>-2.5302</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9999</v>
+        <v>-1.3156</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.2107</v>
+        <v>-0.0791</v>
       </c>
       <c r="K40" t="n">
         <v>202</v>
@@ -2277,7 +2277,7 @@
         <v>96</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.2106</v>
+        <v>-1.3947</v>
       </c>
       <c r="N40" t="n">
         <v>298</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0037</v>
+        <v>-3.0362</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3016</v>
+        <v>-0.3049</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6406</v>
+        <v>-2.0087</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0037</v>
+        <v>-3.0362</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0037</v>
+        <v>-1.4144</v>
       </c>
       <c r="G41" t="n">
-        <v>-2</v>
+        <v>-1.6218</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0037</v>
+        <v>-1.4144</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8135</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-2</v>
+        <v>-1.6218</v>
       </c>
       <c r="K41" t="n">
         <v>44</v>
@@ -2323,7 +2323,7 @@
         <v>147</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.8135</v>
+        <v>-2.3572</v>
       </c>
       <c r="N41" t="n">
         <v>191</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3441</v>
+        <v>0.3751</v>
       </c>
       <c r="J2" t="n">
-        <v>7.9143</v>
+        <v>8.6273</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.171</v>
+        <v>0.1543</v>
       </c>
       <c r="J3" t="n">
-        <v>3.933</v>
+        <v>3.5489</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1527</v>
+        <v>-0.121</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.5121</v>
+        <v>-2.783</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.64</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5707</v>
+        <v>-0.3761</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.1261</v>
+        <v>-8.6503</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6224</v>
+        <v>-0.4135</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.3152</v>
+        <v>-9.5105</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5094</v>
+        <v>1.3293</v>
       </c>
       <c r="J7" t="n">
-        <v>34.7162</v>
+        <v>30.5739</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1596</v>
+        <v>1.1019</v>
       </c>
       <c r="J8" t="n">
-        <v>26.6708</v>
+        <v>25.3437</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2051</v>
+        <v>0.273</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7173</v>
+        <v>6.279</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3612</v>
+        <v>-0.2837</v>
       </c>
       <c r="J10" t="n">
-        <v>-8.307600000000001</v>
+        <v>-6.5251</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5577</v>
+        <v>-0.4894</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.8271</v>
+        <v>-11.2562</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3482</v>
+        <v>0.3859</v>
       </c>
       <c r="J12" t="n">
-        <v>9.749599999999999</v>
+        <v>10.8052</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3176</v>
+        <v>0.3467</v>
       </c>
       <c r="J13" t="n">
-        <v>8.892799999999999</v>
+        <v>9.707599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0989</v>
+        <v>0.08</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7692</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4937</v>
+        <v>-0.3189</v>
       </c>
       <c r="J15" t="n">
-        <v>-13.8236</v>
+        <v>-8.9292</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5853</v>
+        <v>-0.385</v>
       </c>
       <c r="J16" t="n">
-        <v>-16.3884</v>
+        <v>-10.78</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.11</v>
+        <v>1.0685</v>
       </c>
       <c r="J17" t="n">
-        <v>31.08</v>
+        <v>29.918</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5212</v>
+        <v>0.539</v>
       </c>
       <c r="J18" t="n">
-        <v>14.5936</v>
+        <v>15.092</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2465</v>
+        <v>0.3072</v>
       </c>
       <c r="J19" t="n">
-        <v>6.902</v>
+        <v>8.601599999999999</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2465</v>
+        <v>0.3072</v>
       </c>
       <c r="J20" t="n">
-        <v>6.902</v>
+        <v>8.601599999999999</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1561</v>
+        <v>0.2198</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3708</v>
+        <v>6.1544</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.88</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8374</v>
+        <v>1.3458</v>
       </c>
       <c r="J22" t="n">
-        <v>51.4472</v>
+        <v>37.6824</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4512</v>
+        <v>0.4266</v>
       </c>
       <c r="J23" t="n">
-        <v>12.6336</v>
+        <v>11.9448</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1157</v>
+        <v>-0.0436</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.2396</v>
+        <v>-1.2208</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2539</v>
+        <v>-0.1769</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.1092</v>
+        <v>-4.9532</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5244</v>
+        <v>-0.4555</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.6832</v>
+        <v>-12.754</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6097</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>17.0716</v>
+        <v>16.0188</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1561</v>
+        <v>0.1622</v>
       </c>
       <c r="J28" t="n">
-        <v>4.3708</v>
+        <v>4.5416</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1545</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>-4.326</v>
+        <v>-2.4612</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.277</v>
+        <v>-0.1666</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.756</v>
+        <v>-4.6648</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4532</v>
+        <v>-0.2881</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.6896</v>
+        <v>-8.066800000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6966</v>
+        <v>0.5427</v>
       </c>
       <c r="J32" t="n">
-        <v>17.415</v>
+        <v>13.5675</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6209</v>
+        <v>0.5002</v>
       </c>
       <c r="J33" t="n">
-        <v>15.5225</v>
+        <v>12.505</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4109</v>
+        <v>0.3993</v>
       </c>
       <c r="J34" t="n">
-        <v>10.2725</v>
+        <v>9.9825</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.229</v>
+        <v>0.2838</v>
       </c>
       <c r="J35" t="n">
-        <v>5.725</v>
+        <v>7.095</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.08</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1983</v>
+        <v>0.2548</v>
       </c>
       <c r="J36" t="n">
-        <v>4.9575</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.276</v>
+        <v>0.2874</v>
       </c>
       <c r="J37" t="n">
-        <v>6.9</v>
+        <v>7.185</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.06</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2058</v>
+        <v>0.1986</v>
       </c>
       <c r="J38" t="n">
-        <v>5.145</v>
+        <v>4.965</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2976</v>
+        <v>-0.1937</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.44</v>
+        <v>-4.8425</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5063</v>
+        <v>-0.3303</v>
       </c>
       <c r="J40" t="n">
-        <v>-12.6575</v>
+        <v>-8.2575</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5063</v>
+        <v>-0.3303</v>
       </c>
       <c r="J41" t="n">
-        <v>-12.6575</v>
+        <v>-8.2575</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6346000000000001</v>
+        <v>0.4963</v>
       </c>
       <c r="J42" t="n">
-        <v>17.1342</v>
+        <v>13.4001</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3539</v>
+        <v>0.3428</v>
       </c>
       <c r="J43" t="n">
-        <v>9.555300000000001</v>
+        <v>9.255599999999999</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2766</v>
+        <v>0.2964</v>
       </c>
       <c r="J44" t="n">
-        <v>7.4682</v>
+        <v>8.002800000000001</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1024</v>
+        <v>0.1449</v>
       </c>
       <c r="J45" t="n">
-        <v>2.7648</v>
+        <v>3.9123</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0653</v>
+        <v>0.1105</v>
       </c>
       <c r="J46" t="n">
-        <v>1.7631</v>
+        <v>2.9835</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2666</v>
+        <v>0.2835</v>
       </c>
       <c r="J47" t="n">
-        <v>7.1982</v>
+        <v>7.6545</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.25</v>
+        <v>0.2628</v>
       </c>
       <c r="J48" t="n">
-        <v>6.75</v>
+        <v>7.0956</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1597</v>
+        <v>0.1532</v>
       </c>
       <c r="J49" t="n">
-        <v>4.3119</v>
+        <v>4.1364</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2916</v>
+        <v>-0.1812</v>
       </c>
       <c r="J50" t="n">
-        <v>-7.8732</v>
+        <v>-4.8924</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6369</v>
+        <v>-0.4229</v>
       </c>
       <c r="J51" t="n">
-        <v>-17.1963</v>
+        <v>-11.4183</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1653</v>
+        <v>0.1203</v>
       </c>
       <c r="J52" t="n">
-        <v>4.7937</v>
+        <v>3.4887</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0409</v>
+        <v>0.0102</v>
       </c>
       <c r="J53" t="n">
-        <v>1.1861</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0409</v>
+        <v>0.0102</v>
       </c>
       <c r="J54" t="n">
-        <v>1.1861</v>
+        <v>0.2958</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.2701</v>
+        <v>-0.1691</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.8329</v>
+        <v>-4.9039</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.465</v>
+        <v>-0.299</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.485</v>
+        <v>-8.670999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.54</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7468</v>
+        <v>0.5298</v>
       </c>
       <c r="J57" t="n">
-        <v>21.6572</v>
+        <v>15.3642</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.4783</v>
       </c>
       <c r="J58" t="n">
-        <v>18.9863</v>
+        <v>13.8707</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3979</v>
+        <v>0.3438</v>
       </c>
       <c r="J59" t="n">
-        <v>11.5391</v>
+        <v>9.9702</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.014</v>
+        <v>0.0233</v>
       </c>
       <c r="J60" t="n">
-        <v>-0.406</v>
+        <v>0.6757</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4991</v>
+        <v>-0.3184</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.4739</v>
+        <v>-9.233599999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.29</v>
       </c>
       <c r="I62" t="n">
-        <v>0.832</v>
+        <v>0.6132</v>
       </c>
       <c r="J62" t="n">
-        <v>33.28</v>
+        <v>24.528</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.4531</v>
       </c>
       <c r="J63" t="n">
-        <v>22.48</v>
+        <v>18.124</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.13</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4228</v>
+        <v>0.3764</v>
       </c>
       <c r="J64" t="n">
-        <v>16.912</v>
+        <v>15.056</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3286</v>
+        <v>0.323</v>
       </c>
       <c r="J65" t="n">
-        <v>13.144</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8401999999999999</v>
+        <v>-0.7991</v>
       </c>
       <c r="J66" t="n">
-        <v>-33.608</v>
+        <v>-31.964</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.453</v>
+        <v>0.4486</v>
       </c>
       <c r="J67" t="n">
-        <v>18.12</v>
+        <v>17.944</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0029</v>
+        <v>-0.0001</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.116</v>
+        <v>-0.004</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.764</v>
+        <v>-1.444</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2285</v>
+        <v>-0.1345</v>
       </c>
       <c r="J70" t="n">
-        <v>-9.140000000000001</v>
+        <v>-5.38</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2619</v>
+        <v>-0.1564</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.476</v>
+        <v>-6.256</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7877</v>
+        <v>0.9791</v>
       </c>
       <c r="J72" t="n">
-        <v>23.631</v>
+        <v>29.373</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.22</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3895</v>
+        <v>0.4555</v>
       </c>
       <c r="J73" t="n">
-        <v>11.685</v>
+        <v>13.665</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2182</v>
+        <v>0.2522</v>
       </c>
       <c r="J74" t="n">
-        <v>6.546</v>
+        <v>7.566</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.466</v>
+        <v>-0.2956</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.98</v>
+        <v>-8.868</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5185</v>
+        <v>-0.3339</v>
       </c>
       <c r="J76" t="n">
-        <v>-15.555</v>
+        <v>-10.017</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.715</v>
+        <v>0.6872</v>
       </c>
       <c r="J77" t="n">
-        <v>21.45</v>
+        <v>20.616</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4818</v>
+        <v>0.4592</v>
       </c>
       <c r="J78" t="n">
-        <v>14.454</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1805</v>
+        <v>0.211</v>
       </c>
       <c r="J79" t="n">
-        <v>5.415</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0716</v>
+        <v>0.1129</v>
       </c>
       <c r="J80" t="n">
-        <v>2.148</v>
+        <v>3.387</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2841</v>
+        <v>-0.2204</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.523</v>
+        <v>-6.612</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.11</v>
       </c>
       <c r="I82" t="n">
-        <v>0.291</v>
+        <v>0.307</v>
       </c>
       <c r="J82" t="n">
-        <v>7.275</v>
+        <v>7.675</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.89</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1805</v>
+        <v>-0.1333</v>
       </c>
       <c r="J83" t="n">
-        <v>-4.5125</v>
+        <v>-3.3325</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2824</v>
+        <v>-0.1841</v>
       </c>
       <c r="J84" t="n">
-        <v>-7.06</v>
+        <v>-4.6025</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2994</v>
+        <v>-0.1942</v>
       </c>
       <c r="J85" t="n">
-        <v>-7.485</v>
+        <v>-4.855</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4659</v>
+        <v>-0.3022</v>
       </c>
       <c r="J86" t="n">
-        <v>-11.6475</v>
+        <v>-7.555</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1972</v>
+        <v>1.1263</v>
       </c>
       <c r="J87" t="n">
-        <v>29.93</v>
+        <v>28.1575</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8096</v>
+        <v>0.8137</v>
       </c>
       <c r="J88" t="n">
-        <v>20.24</v>
+        <v>20.3425</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7134</v>
+        <v>0.7217</v>
       </c>
       <c r="J89" t="n">
-        <v>17.835</v>
+        <v>18.0425</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2883</v>
+        <v>0.3555</v>
       </c>
       <c r="J90" t="n">
-        <v>7.2075</v>
+        <v>8.887499999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5851</v>
+        <v>-0.5184</v>
       </c>
       <c r="J91" t="n">
-        <v>-14.6275</v>
+        <v>-12.96</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.13</v>
       </c>
       <c r="I92" t="n">
-        <v>0.2849</v>
+        <v>0.3119</v>
       </c>
       <c r="J92" t="n">
-        <v>11.9658</v>
+        <v>13.0998</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1441</v>
+        <v>0.1436</v>
       </c>
       <c r="J93" t="n">
-        <v>6.0522</v>
+        <v>6.0312</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.03</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1019</v>
+        <v>0.0956</v>
       </c>
       <c r="J94" t="n">
-        <v>4.2798</v>
+        <v>4.0152</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2036</v>
+        <v>-0.1209</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.5512</v>
+        <v>-5.0778</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4075</v>
+        <v>-0.2566</v>
       </c>
       <c r="J96" t="n">
-        <v>-17.115</v>
+        <v>-10.7772</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.4277</v>
+        <v>1.2727</v>
       </c>
       <c r="J97" t="n">
-        <v>59.9634</v>
+        <v>53.4534</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4099</v>
+        <v>0.4022</v>
       </c>
       <c r="J98" t="n">
-        <v>17.2158</v>
+        <v>16.8924</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1415</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.943</v>
+        <v>-3.3054</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3859</v>
+        <v>-0.3192</v>
       </c>
       <c r="J100" t="n">
-        <v>-16.2078</v>
+        <v>-13.4064</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4439</v>
+        <v>-0.3783</v>
       </c>
       <c r="J101" t="n">
-        <v>-18.6438</v>
+        <v>-15.8886</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.87</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0958</v>
+        <v>1.0024</v>
       </c>
       <c r="J102" t="n">
-        <v>31.7782</v>
+        <v>29.0696</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2187</v>
+        <v>0.2202</v>
       </c>
       <c r="J103" t="n">
-        <v>6.3423</v>
+        <v>6.3858</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0095</v>
+        <v>0.043</v>
       </c>
       <c r="J104" t="n">
-        <v>0.2755</v>
+        <v>1.247</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1277</v>
+        <v>-0.0553</v>
       </c>
       <c r="J105" t="n">
-        <v>-3.7033</v>
+        <v>-1.6037</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.188</v>
+        <v>-0.096</v>
       </c>
       <c r="J106" t="n">
-        <v>-5.452</v>
+        <v>-2.784</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4443</v>
+        <v>0.3896</v>
       </c>
       <c r="J107" t="n">
-        <v>12.8847</v>
+        <v>11.2984</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.0756</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.3258</v>
+        <v>-2.1924</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.3456</v>
+        <v>-0.2234</v>
       </c>
       <c r="J109" t="n">
-        <v>-10.0224</v>
+        <v>-6.4786</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4501</v>
+        <v>-0.2917</v>
       </c>
       <c r="J110" t="n">
-        <v>-13.0529</v>
+        <v>-8.459300000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5194</v>
+        <v>-0.3395</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.0626</v>
+        <v>-9.845499999999999</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4132</v>
+        <v>0.4678</v>
       </c>
       <c r="J112" t="n">
-        <v>10.7432</v>
+        <v>12.1628</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.93</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0533</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.3858</v>
+        <v>-1.7966</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.71</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.4426</v>
+        <v>-0.2968</v>
       </c>
       <c r="J114" t="n">
-        <v>-11.5076</v>
+        <v>-7.7168</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6781</v>
+        <v>-0.4562</v>
       </c>
       <c r="J115" t="n">
-        <v>-17.6306</v>
+        <v>-11.8612</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7161</v>
+        <v>-0.4841</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.6186</v>
+        <v>-12.5866</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.8646</v>
+        <v>1.573</v>
       </c>
       <c r="J117" t="n">
-        <v>48.4796</v>
+        <v>40.898</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8834</v>
+        <v>0.8952</v>
       </c>
       <c r="J118" t="n">
-        <v>22.9684</v>
+        <v>23.2752</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.4877</v>
+        <v>0.5535</v>
       </c>
       <c r="J119" t="n">
-        <v>12.6802</v>
+        <v>14.391</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.3277</v>
+        <v>0.4018</v>
       </c>
       <c r="J120" t="n">
-        <v>8.520200000000001</v>
+        <v>10.4468</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.048</v>
+        <v>-1.0291</v>
       </c>
       <c r="J121" t="n">
-        <v>-27.248</v>
+        <v>-26.7566</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4523</v>
+        <v>0.5202</v>
       </c>
       <c r="J122" t="n">
-        <v>9.9506</v>
+        <v>11.4444</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2739</v>
+        <v>-0.198</v>
       </c>
       <c r="J123" t="n">
-        <v>-6.0258</v>
+        <v>-4.356</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3852</v>
+        <v>-0.2554</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.474399999999999</v>
+        <v>-5.6188</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.4313</v>
+        <v>-0.2842</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.4886</v>
+        <v>-6.2524</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6503</v>
+        <v>-0.4349</v>
       </c>
       <c r="J126" t="n">
-        <v>-14.3066</v>
+        <v>-9.5678</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.913</v>
+        <v>1.613</v>
       </c>
       <c r="J127" t="n">
-        <v>42.086</v>
+        <v>35.486</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.69</v>
       </c>
       <c r="I128" t="n">
-        <v>1.5023</v>
+        <v>1.3342</v>
       </c>
       <c r="J128" t="n">
-        <v>33.0506</v>
+        <v>29.3524</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5651</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="J129" t="n">
-        <v>12.4322</v>
+        <v>14.6916</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4707</v>
+        <v>0.5728</v>
       </c>
       <c r="J130" t="n">
-        <v>10.3554</v>
+        <v>12.6016</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.744</v>
+        <v>-0.6882</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.368</v>
+        <v>-15.1404</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.08</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2248</v>
+        <v>0.228</v>
       </c>
       <c r="J132" t="n">
-        <v>6.5192</v>
+        <v>6.612</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0549</v>
       </c>
       <c r="J133" t="n">
-        <v>2.3258</v>
+        <v>1.5921</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1037</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.0073</v>
+        <v>-2.3548</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3152</v>
+        <v>-0.1989</v>
       </c>
       <c r="J135" t="n">
-        <v>-9.1408</v>
+        <v>-5.7681</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.4626</v>
+        <v>-0.2977</v>
       </c>
       <c r="J136" t="n">
-        <v>-13.4154</v>
+        <v>-8.6333</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1849</v>
+        <v>1.1172</v>
       </c>
       <c r="J137" t="n">
-        <v>34.3621</v>
+        <v>32.3988</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.25</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6738</v>
+        <v>0.6788999999999999</v>
       </c>
       <c r="J138" t="n">
-        <v>19.5402</v>
+        <v>19.6881</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.15</v>
       </c>
       <c r="I139" t="n">
-        <v>0.3818</v>
+        <v>0.4383</v>
       </c>
       <c r="J139" t="n">
-        <v>11.0722</v>
+        <v>12.7107</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.18</v>
+        <v>0.2463</v>
       </c>
       <c r="J140" t="n">
-        <v>5.22</v>
+        <v>7.1427</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.01</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.0625</v>
+        <v>0.0078</v>
       </c>
       <c r="J141" t="n">
-        <v>-1.8125</v>
+        <v>0.2262</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.77</v>
       </c>
       <c r="I142" t="n">
-        <v>1.6635</v>
+        <v>1.437</v>
       </c>
       <c r="J142" t="n">
-        <v>36.597</v>
+        <v>31.614</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.59</v>
       </c>
       <c r="I143" t="n">
-        <v>1.3307</v>
+        <v>1.2222</v>
       </c>
       <c r="J143" t="n">
-        <v>29.2754</v>
+        <v>26.8884</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.3878</v>
+        <v>0.4822</v>
       </c>
       <c r="J144" t="n">
-        <v>8.531599999999999</v>
+        <v>10.6084</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.18</v>
+        <v>0.269</v>
       </c>
       <c r="J145" t="n">
-        <v>3.96</v>
+        <v>5.918</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.08</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1238</v>
+        <v>0.211</v>
       </c>
       <c r="J146" t="n">
-        <v>2.7236</v>
+        <v>4.642</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3188</v>
+        <v>0.3405</v>
       </c>
       <c r="J147" t="n">
-        <v>7.0136</v>
+        <v>7.491</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.77</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.3061</v>
+        <v>-0.2365</v>
       </c>
       <c r="J148" t="n">
-        <v>-6.7342</v>
+        <v>-5.203</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.75</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.3409</v>
+        <v>-0.2556</v>
       </c>
       <c r="J149" t="n">
-        <v>-7.4998</v>
+        <v>-5.6232</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.4554</v>
+        <v>-0.3103</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.0188</v>
+        <v>-6.8266</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.891</v>
+        <v>-0.6175</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.602</v>
+        <v>-13.585</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.14</v>
       </c>
       <c r="I152" t="n">
-        <v>0.3418</v>
+        <v>0.2849</v>
       </c>
       <c r="J152" t="n">
-        <v>9.2286</v>
+        <v>7.6923</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0793</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.1411</v>
+        <v>-2.0331</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.137</v>
+        <v>-0.1106</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.699</v>
+        <v>-2.9862</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3288</v>
+        <v>-0.2132</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.877599999999999</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6861</v>
+        <v>-0.4604</v>
       </c>
       <c r="J156" t="n">
-        <v>-18.5247</v>
+        <v>-12.4308</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>0.7726</v>
+        <v>0.6925</v>
       </c>
       <c r="J157" t="n">
-        <v>20.8602</v>
+        <v>18.6975</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4441</v>
+        <v>0.3949</v>
       </c>
       <c r="J158" t="n">
-        <v>11.9907</v>
+        <v>10.6623</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3164</v>
+        <v>0.3031</v>
       </c>
       <c r="J159" t="n">
-        <v>8.5428</v>
+        <v>8.1837</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0216</v>
+        <v>0.056</v>
       </c>
       <c r="J160" t="n">
-        <v>0.5832000000000001</v>
+        <v>1.512</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0016</v>
+        <v>0.0385</v>
       </c>
       <c r="J161" t="n">
-        <v>0.0432</v>
+        <v>1.0395</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5357</v>
+        <v>1.3491</v>
       </c>
       <c r="J162" t="n">
-        <v>42.9996</v>
+        <v>37.7748</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1494</v>
+        <v>1.1015</v>
       </c>
       <c r="J163" t="n">
-        <v>32.1832</v>
+        <v>30.842</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2627</v>
+        <v>0.3426</v>
       </c>
       <c r="J164" t="n">
-        <v>7.3556</v>
+        <v>9.5928</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.03</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.0091</v>
+        <v>0.0683</v>
       </c>
       <c r="J165" t="n">
-        <v>-0.2548</v>
+        <v>1.9124</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.0461</v>
+        <v>0.0312</v>
       </c>
       <c r="J166" t="n">
-        <v>-1.2908</v>
+        <v>0.8736</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6904</v>
+        <v>0.8517</v>
       </c>
       <c r="J167" t="n">
-        <v>19.3312</v>
+        <v>23.8476</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0495</v>
+        <v>0.0185</v>
       </c>
       <c r="J168" t="n">
-        <v>1.386</v>
+        <v>0.518</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2954</v>
+        <v>-0.1875</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.2712</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3884</v>
+        <v>-0.2477</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.8752</v>
+        <v>-6.9356</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.5013</v>
       </c>
       <c r="J171" t="n">
-        <v>-20.7312</v>
+        <v>-14.0364</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6151</v>
+        <v>0.7569</v>
       </c>
       <c r="J172" t="n">
-        <v>12.9171</v>
+        <v>15.8949</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.3419</v>
+        <v>-0.2489</v>
       </c>
       <c r="J173" t="n">
-        <v>-7.1799</v>
+        <v>-5.2269</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.3857</v>
+        <v>-0.2669</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.0997</v>
+        <v>-5.6049</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.467</v>
+        <v>-0.3137</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.807</v>
+        <v>-6.5877</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.9747</v>
+        <v>-0.6844</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.4687</v>
+        <v>-14.3724</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.07</v>
       </c>
       <c r="I177" t="n">
-        <v>2.0361</v>
+        <v>1.7509</v>
       </c>
       <c r="J177" t="n">
-        <v>42.7581</v>
+        <v>36.7689</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.83</v>
       </c>
       <c r="I178" t="n">
-        <v>1.7213</v>
+        <v>1.4811</v>
       </c>
       <c r="J178" t="n">
-        <v>36.1473</v>
+        <v>31.1031</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.45</v>
       </c>
       <c r="I179" t="n">
-        <v>0.9651999999999999</v>
+        <v>1.0374</v>
       </c>
       <c r="J179" t="n">
-        <v>20.2692</v>
+        <v>21.7854</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6042</v>
+        <v>0.7217</v>
       </c>
       <c r="J180" t="n">
-        <v>12.6882</v>
+        <v>15.1557</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.65</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.0988</v>
+        <v>-1.0896</v>
       </c>
       <c r="J181" t="n">
-        <v>-23.0748</v>
+        <v>-22.8816</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.09</v>
       </c>
       <c r="I182" t="n">
-        <v>2.049</v>
+        <v>1.7674</v>
       </c>
       <c r="J182" t="n">
-        <v>40.98</v>
+        <v>35.348</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.97</v>
       </c>
       <c r="I183" t="n">
-        <v>1.9334</v>
+        <v>1.6342</v>
       </c>
       <c r="J183" t="n">
-        <v>38.668</v>
+        <v>32.684</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.3918</v>
+        <v>0.5033</v>
       </c>
       <c r="J184" t="n">
-        <v>7.836</v>
+        <v>10.066</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.11</v>
       </c>
       <c r="I185" t="n">
-        <v>0.1694</v>
+        <v>0.2681</v>
       </c>
       <c r="J185" t="n">
-        <v>3.388</v>
+        <v>5.362</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.0654</v>
+        <v>0.0217</v>
       </c>
       <c r="J186" t="n">
-        <v>-1.308</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2253</v>
+        <v>0.2161</v>
       </c>
       <c r="J187" t="n">
-        <v>4.506</v>
+        <v>4.322</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1761</v>
+        <v>-0.1545</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.522</v>
+        <v>-3.09</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.3259</v>
+        <v>-0.2467</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.518</v>
+        <v>-4.934</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5327</v>
+        <v>-0.3576</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.654</v>
+        <v>-7.152</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.39</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8561</v>
+        <v>-0.5903</v>
       </c>
       <c r="J191" t="n">
-        <v>-17.122</v>
+        <v>-11.806</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.33</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5444</v>
+        <v>0.6525</v>
       </c>
       <c r="J192" t="n">
-        <v>12.5212</v>
+        <v>15.0075</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.425</v>
+        <v>0.4971</v>
       </c>
       <c r="J193" t="n">
-        <v>9.775</v>
+        <v>11.4333</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2275</v>
+        <v>0.2564</v>
       </c>
       <c r="J194" t="n">
-        <v>5.2325</v>
+        <v>5.8972</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0264</v>
+        <v>-0.0034</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.6072</v>
+        <v>-0.07820000000000001</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.7226</v>
+        <v>-0.4877</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.6198</v>
+        <v>-11.2171</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8752</v>
+        <v>0.8801</v>
       </c>
       <c r="J197" t="n">
-        <v>20.1296</v>
+        <v>20.2423</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.31</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8061</v>
+        <v>0.8121</v>
       </c>
       <c r="J198" t="n">
-        <v>18.5403</v>
+        <v>18.6783</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5738</v>
+        <v>0.6046</v>
       </c>
       <c r="J199" t="n">
-        <v>13.1974</v>
+        <v>13.9058</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.2853</v>
+        <v>0.3542</v>
       </c>
       <c r="J200" t="n">
-        <v>6.5619</v>
+        <v>8.146599999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.1996</v>
+        <v>0.2702</v>
       </c>
       <c r="J201" t="n">
-        <v>4.5908</v>
+        <v>6.2146</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8061</v>
+        <v>0.7746</v>
       </c>
       <c r="J202" t="n">
-        <v>33.8562</v>
+        <v>32.5332</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.6105</v>
+        <v>0.5739</v>
       </c>
       <c r="J203" t="n">
-        <v>25.641</v>
+        <v>24.1038</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0969</v>
+        <v>0.1205</v>
       </c>
       <c r="J204" t="n">
-        <v>4.0698</v>
+        <v>5.061</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2672</v>
+        <v>-0.2111</v>
       </c>
       <c r="J205" t="n">
-        <v>-11.2224</v>
+        <v>-8.866199999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6372</v>
+        <v>-0.584</v>
       </c>
       <c r="J206" t="n">
-        <v>-26.7624</v>
+        <v>-24.528</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4018</v>
+        <v>0.4657</v>
       </c>
       <c r="J207" t="n">
-        <v>16.8756</v>
+        <v>19.5594</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.09</v>
       </c>
       <c r="I208" t="n">
-        <v>0.1983</v>
+        <v>0.2192</v>
       </c>
       <c r="J208" t="n">
-        <v>8.3286</v>
+        <v>9.2064</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.016</v>
+        <v>0.0343</v>
       </c>
       <c r="J209" t="n">
-        <v>0.672</v>
+        <v>1.4406</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0559</v>
+        <v>-0.023</v>
       </c>
       <c r="J210" t="n">
-        <v>-2.3478</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.3318</v>
+        <v>-0.2018</v>
       </c>
       <c r="J211" t="n">
-        <v>-13.9356</v>
+        <v>-8.4756</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3886</v>
+        <v>0.4333</v>
       </c>
       <c r="J212" t="n">
-        <v>8.160600000000001</v>
+        <v>9.099299999999999</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2007</v>
+        <v>0.1853</v>
       </c>
       <c r="J213" t="n">
-        <v>4.2147</v>
+        <v>3.8913</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.6</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.6056</v>
+        <v>-0.4036</v>
       </c>
       <c r="J214" t="n">
-        <v>-12.7176</v>
+        <v>-8.4756</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.6188</v>
+        <v>-0.4129</v>
       </c>
       <c r="J215" t="n">
-        <v>-12.9948</v>
+        <v>-8.6709</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.58</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6318</v>
+        <v>-0.4222</v>
       </c>
       <c r="J216" t="n">
-        <v>-13.2678</v>
+        <v>-8.866199999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.82</v>
       </c>
       <c r="I217" t="n">
-        <v>1.7569</v>
+        <v>1.4988</v>
       </c>
       <c r="J217" t="n">
-        <v>36.8949</v>
+        <v>31.4748</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>1.054</v>
+        <v>1.0519</v>
       </c>
       <c r="J218" t="n">
-        <v>22.134</v>
+        <v>22.0899</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.637</v>
+        <v>0.7237</v>
       </c>
       <c r="J219" t="n">
-        <v>13.377</v>
+        <v>15.1977</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.442</v>
+        <v>0.5347</v>
       </c>
       <c r="J220" t="n">
-        <v>9.282</v>
+        <v>11.2287</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.91</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4829</v>
+        <v>-0.405</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.1409</v>
+        <v>-8.505000000000001</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.31</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5161</v>
+        <v>0.6158</v>
       </c>
       <c r="J222" t="n">
-        <v>14.4508</v>
+        <v>17.2424</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2242</v>
+        <v>0.2548</v>
       </c>
       <c r="J223" t="n">
-        <v>6.2776</v>
+        <v>7.1344</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0646</v>
+        <v>-0.0251</v>
       </c>
       <c r="J224" t="n">
-        <v>-1.8088</v>
+        <v>-0.7028</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.09</v>
+        <v>-0.0408</v>
       </c>
       <c r="J225" t="n">
-        <v>-2.52</v>
+        <v>-1.1424</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.87</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.2911</v>
+        <v>-0.1727</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.1508</v>
+        <v>-4.8356</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.8038</v>
+        <v>0.7729</v>
       </c>
       <c r="J227" t="n">
-        <v>22.5064</v>
+        <v>21.6412</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7565</v>
+        <v>0.7236</v>
       </c>
       <c r="J228" t="n">
-        <v>21.182</v>
+        <v>20.2608</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1729</v>
+        <v>0.1856</v>
       </c>
       <c r="J229" t="n">
-        <v>4.8412</v>
+        <v>5.1968</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2348</v>
+        <v>-0.179</v>
       </c>
       <c r="J230" t="n">
-        <v>-6.5744</v>
+        <v>-5.012</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.8078</v>
+        <v>-0.7654</v>
       </c>
       <c r="J231" t="n">
-        <v>-22.6184</v>
+        <v>-21.4312</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3427/event_3427_evp_summary.xlsx
+++ b/database/event/3427/event_3427_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3674</v>
+        <v>5.4492</v>
       </c>
       <c r="C2" t="n">
-        <v>0.539</v>
+        <v>0.5472</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7851</v>
+        <v>1.8564</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3674</v>
+        <v>5.4492</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3287</v>
+        <v>2.3021</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0387</v>
+        <v>3.1471</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7187</v>
+        <v>2.7012</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4136</v>
+        <v>1.4586</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0387</v>
+        <v>3.1471</v>
       </c>
       <c r="K2" t="n">
         <v>48</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>4.4523</v>
+        <v>4.6057</v>
       </c>
       <c r="N2" t="n">
         <v>152</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.8846</v>
+        <v>4.913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4905</v>
+        <v>0.4933</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5671</v>
+        <v>1.6123</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8846</v>
+        <v>4.913</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8617</v>
+        <v>2.8634</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0229</v>
+        <v>2.0496</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5967</v>
+        <v>4.5532</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3901</v>
+        <v>2.4587</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0229</v>
+        <v>2.0496</v>
       </c>
       <c r="K3" t="n">
         <v>48</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>4.413</v>
+        <v>4.5083</v>
       </c>
       <c r="N3" t="n">
         <v>152</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3444</v>
+        <v>4.3783</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4362</v>
+        <v>0.4396</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3233</v>
+        <v>1.3689</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3444</v>
+        <v>4.3783</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2537</v>
+        <v>2.1746</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0907</v>
+        <v>2.2037</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4544</v>
+        <v>2.2808</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2762</v>
+        <v>1.2316</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0907</v>
+        <v>2.2037</v>
       </c>
       <c r="K4" t="n">
         <v>48</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3669</v>
+        <v>3.4353</v>
       </c>
       <c r="N4" t="n">
         <v>152</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1603</v>
+        <v>4.1605</v>
       </c>
       <c r="C5" t="n">
         <v>0.4178</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2402</v>
+        <v>1.2697</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1603</v>
+        <v>4.1605</v>
       </c>
       <c r="F5" t="n">
-        <v>3.3008</v>
+        <v>3.2414</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8595</v>
+        <v>0.9191</v>
       </c>
       <c r="H5" t="n">
-        <v>6.1436</v>
+        <v>5.8005</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1944</v>
+        <v>3.1322</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8595</v>
+        <v>0.9191</v>
       </c>
       <c r="K5" t="n">
         <v>129</v>
@@ -667,7 +667,7 @@
         <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0539</v>
+        <v>4.0513</v>
       </c>
       <c r="N5" t="n">
         <v>182</v>
@@ -676,35 +676,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>valde</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.1098</v>
+        <v>4.0951</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4127</v>
+        <v>0.4112</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2174</v>
+        <v>1.24</v>
       </c>
       <c r="E6" t="n">
-        <v>4.1098</v>
+        <v>4.0951</v>
       </c>
       <c r="F6" t="n">
-        <v>3.1642</v>
+        <v>3.2051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9456</v>
+        <v>0.89</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6624</v>
+        <v>5.6806</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9442</v>
+        <v>3.0675</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9456</v>
+        <v>0.89</v>
       </c>
       <c r="K6" t="n">
         <v>202</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8898</v>
+        <v>3.9575</v>
       </c>
       <c r="N6" t="n">
         <v>298</v>
@@ -722,35 +722,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>valde</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0846</v>
+        <v>4.0931</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4101</v>
+        <v>0.411</v>
       </c>
       <c r="D7" t="n">
-        <v>1.206</v>
+        <v>1.2391</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0846</v>
+        <v>4.0931</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2714</v>
+        <v>3.0712</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8132</v>
+        <v>1.0219</v>
       </c>
       <c r="H7" t="n">
-        <v>6.04</v>
+        <v>5.2388</v>
       </c>
       <c r="I7" t="n">
-        <v>3.1405</v>
+        <v>2.8289</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8132</v>
+        <v>1.0219</v>
       </c>
       <c r="K7" t="n">
         <v>202</v>
@@ -759,7 +759,7 @@
         <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9537</v>
+        <v>3.8508</v>
       </c>
       <c r="N7" t="n">
         <v>298</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9383</v>
+        <v>3.9654</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3955</v>
+        <v>0.3982</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1399</v>
+        <v>1.1809</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9383</v>
+        <v>3.9654</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9425</v>
+        <v>2.936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9958</v>
+        <v>1.0294</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8814</v>
+        <v>4.7927</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5381</v>
+        <v>2.588</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9958</v>
+        <v>1.0294</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -805,7 +805,7 @@
         <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5339</v>
+        <v>3.6174</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.655</v>
+        <v>3.6078</v>
       </c>
       <c r="C9" t="n">
-        <v>0.367</v>
+        <v>0.3623</v>
       </c>
       <c r="D9" t="n">
-        <v>1.012</v>
+        <v>1.0181</v>
       </c>
       <c r="E9" t="n">
-        <v>3.655</v>
+        <v>3.6078</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3943</v>
+        <v>2.3081</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2607</v>
+        <v>1.2997</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9499</v>
+        <v>2.721</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5338</v>
+        <v>1.4693</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2607</v>
+        <v>1.2997</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>147</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7945</v>
+        <v>2.769</v>
       </c>
       <c r="N9" t="n">
         <v>191</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6175</v>
+        <v>3.5388</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3632</v>
+        <v>0.3553</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9951</v>
+        <v>0.9867</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6175</v>
+        <v>3.5388</v>
       </c>
       <c r="F10" t="n">
-        <v>3.707</v>
+        <v>3.2805</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0895</v>
+        <v>0.2583</v>
       </c>
       <c r="H10" t="n">
-        <v>7.5747</v>
+        <v>5.9294</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9385</v>
+        <v>3.2018</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0895</v>
+        <v>0.2583</v>
       </c>
       <c r="K10" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L10" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M10" t="n">
-        <v>3.849</v>
+        <v>3.4601</v>
       </c>
       <c r="N10" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6084</v>
+        <v>3.5356</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3623</v>
+        <v>0.355</v>
       </c>
       <c r="D11" t="n">
-        <v>0.991</v>
+        <v>0.9853</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6084</v>
+        <v>3.5356</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3584</v>
+        <v>3.6395</v>
       </c>
       <c r="G11" t="n">
-        <v>0.25</v>
+        <v>-0.1039</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3467</v>
+        <v>7.114</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3</v>
+        <v>3.8415</v>
       </c>
       <c r="J11" t="n">
-        <v>0.25</v>
+        <v>-0.1039</v>
       </c>
       <c r="K11" t="n">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="L11" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.7376</v>
       </c>
       <c r="N11" t="n">
-        <v>298</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5092</v>
+        <v>3.5178</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3524</v>
+        <v>0.3532</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9462</v>
+        <v>0.9772</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5092</v>
+        <v>3.5178</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5104</v>
+        <v>2.4695</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9988</v>
+        <v>1.0483</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3586</v>
+        <v>3.2536</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7463</v>
+        <v>1.7569</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9988</v>
+        <v>1.0483</v>
       </c>
       <c r="K12" t="n">
         <v>44</v>
@@ -989,7 +989,7 @@
         <v>147</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7451</v>
+        <v>2.8052</v>
       </c>
       <c r="N12" t="n">
         <v>191</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5775</v>
+        <v>2.5015</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2588</v>
+        <v>0.2512</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5256</v>
+        <v>0.5145</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5775</v>
+        <v>2.5015</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4534</v>
+        <v>2.3707</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1241</v>
+        <v>0.1308</v>
       </c>
       <c r="H13" t="n">
-        <v>3.158</v>
+        <v>2.9276</v>
       </c>
       <c r="I13" t="n">
-        <v>1.642</v>
+        <v>1.5809</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1241</v>
+        <v>0.1308</v>
       </c>
       <c r="K13" t="n">
         <v>44</v>
@@ -1035,7 +1035,7 @@
         <v>147</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7661</v>
+        <v>1.7117</v>
       </c>
       <c r="N13" t="n">
         <v>191</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2188</v>
+        <v>2.1592</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2228</v>
+        <v>0.2168</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3637</v>
+        <v>0.3587</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2188</v>
+        <v>2.1592</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3869</v>
+        <v>2.3335</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1681</v>
+        <v>-0.1743</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9235</v>
+        <v>2.805</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5201</v>
+        <v>1.5147</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1681</v>
+        <v>-0.1743</v>
       </c>
       <c r="K14" t="n">
         <v>129</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.352</v>
+        <v>1.3404</v>
       </c>
       <c r="N14" t="n">
         <v>182</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1936</v>
+        <v>0.1829</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2322</v>
+        <v>0.2052</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9277</v>
+        <v>1.8219</v>
       </c>
       <c r="N15" t="n">
         <v>97</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1814</v>
+        <v>0.1763</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1774</v>
+        <v>0.1752</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8063</v>
+        <v>1.7561</v>
       </c>
       <c r="N16" t="n">
         <v>119</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6801</v>
+        <v>1.5329</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1687</v>
+        <v>0.1539</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1205</v>
+        <v>0.0736</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6801</v>
+        <v>1.5329</v>
       </c>
       <c r="F17" t="n">
-        <v>2.177</v>
+        <v>2.0576</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4969</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.184</v>
+        <v>2.0576</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1356</v>
+        <v>1.1111</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4969</v>
+        <v>-0.5247000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>129</v>
@@ -1219,7 +1219,7 @@
         <v>53</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6386999999999999</v>
+        <v>0.5863999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>182</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5861</v>
+        <v>1.5087</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1593</v>
+        <v>0.1515</v>
       </c>
       <c r="D18" t="n">
-        <v>0.078</v>
+        <v>0.0626</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5861</v>
+        <v>1.5087</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2421</v>
+        <v>2.2009</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.656</v>
+        <v>-0.6922</v>
       </c>
       <c r="H18" t="n">
-        <v>2.4135</v>
+        <v>2.3674</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2549</v>
+        <v>1.2784</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.656</v>
+        <v>-0.6922</v>
       </c>
       <c r="K18" t="n">
         <v>202</v>
@@ -1265,7 +1265,7 @@
         <v>96</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5988999999999999</v>
+        <v>0.5861999999999999</v>
       </c>
       <c r="N18" t="n">
         <v>298</v>
@@ -1274,93 +1274,93 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4295</v>
+        <v>1.3657</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1435</v>
+        <v>0.1371</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0073</v>
+        <v>-0.0025</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4295</v>
+        <v>1.3657</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4295</v>
+        <v>1.6752</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3095</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4295</v>
+        <v>1.6752</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4295</v>
+        <v>0.9046</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3095</v>
       </c>
       <c r="K19" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4295</v>
+        <v>0.5951</v>
       </c>
       <c r="N19" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3784</v>
+        <v>1.3408</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1384</v>
+        <v>0.1346</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0157</v>
+        <v>-0.0138</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3784</v>
+        <v>1.3408</v>
       </c>
       <c r="F20" t="n">
-        <v>1.66</v>
+        <v>1.3408</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2816</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.66</v>
+        <v>1.3408</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8631</v>
+        <v>1.3408</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2816</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="L20" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5814999999999999</v>
+        <v>1.3408</v>
       </c>
       <c r="N20" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1021</v>
+        <v>1.2422</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1107</v>
+        <v>0.1247</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1405</v>
+        <v>-0.0587</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1021</v>
+        <v>1.2422</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8726</v>
+        <v>0.898</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2295</v>
+        <v>0.3442</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8726</v>
+        <v>0.898</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4537</v>
+        <v>0.4849</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2295</v>
+        <v>0.3442</v>
       </c>
       <c r="K21" t="n">
         <v>48</v>
@@ -1403,7 +1403,7 @@
         <v>104</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6832</v>
+        <v>0.8290999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06510000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3232</v>
+        <v>-0.3292</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6973</v>
+        <v>0.6481</v>
       </c>
       <c r="N22" t="n">
         <v>97</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0465</v>
+        <v>0.0426</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4289</v>
+        <v>-0.4311</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4633</v>
+        <v>0.4241</v>
       </c>
       <c r="N23" t="n">
         <v>72</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0423</v>
+        <v>0.0361</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4478</v>
+        <v>-0.4607</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4214</v>
+        <v>0.3591</v>
       </c>
       <c r="N24" t="n">
         <v>97</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0409</v>
+        <v>0.0358</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4539</v>
+        <v>-0.4617</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4078</v>
+        <v>0.3569</v>
       </c>
       <c r="N25" t="n">
         <v>72</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0286</v>
+        <v>0.0272</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5095</v>
+        <v>-0.5009</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2846</v>
+        <v>0.2708</v>
       </c>
       <c r="N26" t="n">
         <v>119</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0202</v>
+        <v>0.016</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.547</v>
+        <v>-0.5516</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2015</v>
+        <v>0.1595</v>
       </c>
       <c r="N27" t="n">
         <v>159</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0142</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5743</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1411</v>
+        <v>0.0878</v>
       </c>
       <c r="N28" t="n">
         <v>97</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004</v>
+        <v>-0.0017</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6364</v>
+        <v>-0.6318</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.0036</v>
+        <v>-0.0166</v>
       </c>
       <c r="N29" t="n">
         <v>97</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0007</v>
+        <v>-0.0057</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6412</v>
+        <v>-0.6502</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.0071</v>
+        <v>-0.057</v>
       </c>
       <c r="N30" t="n">
         <v>119</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0447</v>
+        <v>-0.0469</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8391999999999999</v>
+        <v>-0.837</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4456</v>
+        <v>-0.4674</v>
       </c>
       <c r="N31" t="n">
         <v>159</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.046</v>
+        <v>-0.0472</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8446</v>
+        <v>-0.8383</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4577</v>
+        <v>-0.4703</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0512</v>
+        <v>-0.0585</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.868</v>
+        <v>-0.8895</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5095</v>
+        <v>-0.5827</v>
       </c>
       <c r="N33" t="n">
         <v>159</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0688</v>
+        <v>-0.0664</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9475</v>
+        <v>-0.925</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6855</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>159</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0743</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9722</v>
+        <v>-0.9811</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7402</v>
+        <v>-0.7841</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0796</v>
+        <v>-0.079</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9957</v>
+        <v>-0.9825</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7924</v>
+        <v>-0.7871</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0806</v>
+        <v>-0.0829</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0002</v>
+        <v>-0.9999</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8022</v>
+        <v>-0.8252</v>
       </c>
       <c r="N37" t="n">
         <v>72</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.09</v>
+        <v>-0.0946</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0425</v>
+        <v>-1.053</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.896</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>72</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3621</v>
+        <v>-1.0373</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1368</v>
+        <v>-0.1042</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2529</v>
+        <v>-1.0964</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3621</v>
+        <v>-1.0373</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4303</v>
+        <v>-1.2067</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0682</v>
+        <v>0.1694</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4303</v>
+        <v>-1.2067</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7437</v>
+        <v>-0.6516</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0682</v>
+        <v>0.1694</v>
       </c>
       <c r="K39" t="n">
         <v>48</v>
@@ -2231,7 +2231,7 @@
         <v>104</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6755</v>
+        <v>-0.4822</v>
       </c>
       <c r="N39" t="n">
         <v>152</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.6093</v>
+        <v>-2.2382</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.262</v>
+        <v>-0.2247</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.816</v>
+        <v>-1.6431</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.6093</v>
+        <v>-2.2382</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.5302</v>
+        <v>-2.2045</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0791</v>
+        <v>-0.0337</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.5302</v>
+        <v>-2.2045</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3156</v>
+        <v>-1.1904</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0791</v>
+        <v>-0.0337</v>
       </c>
       <c r="K40" t="n">
         <v>202</v>
@@ -2277,7 +2277,7 @@
         <v>96</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3947</v>
+        <v>-1.2241</v>
       </c>
       <c r="N40" t="n">
         <v>298</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-3.0362</v>
+        <v>-2.7424</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3049</v>
+        <v>-0.2754</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.0087</v>
+        <v>-1.8726</v>
       </c>
       <c r="E41" t="n">
-        <v>-3.0362</v>
+        <v>-2.7424</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.4144</v>
+        <v>-1.1528</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.6218</v>
+        <v>-1.5896</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.4144</v>
+        <v>-1.1528</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7354000000000001</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.6218</v>
+        <v>-1.5896</v>
       </c>
       <c r="K41" t="n">
         <v>44</v>
@@ -2323,7 +2323,7 @@
         <v>147</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3572</v>
+        <v>-2.2121</v>
       </c>
       <c r="N41" t="n">
         <v>191</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3751</v>
+        <v>0.3642</v>
       </c>
       <c r="J2" t="n">
-        <v>8.6273</v>
+        <v>8.3766</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1543</v>
+        <v>0.1524</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5489</v>
+        <v>3.5052</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.121</v>
+        <v>-0.1368</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.783</v>
+        <v>-3.1464</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.64</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3761</v>
+        <v>-0.3891</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.6503</v>
+        <v>-8.949299999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4135</v>
+        <v>-0.4248</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.5105</v>
+        <v>-9.7704</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3293</v>
+        <v>1.4102</v>
       </c>
       <c r="J7" t="n">
-        <v>30.5739</v>
+        <v>32.4346</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.1019</v>
+        <v>1.0823</v>
       </c>
       <c r="J8" t="n">
-        <v>25.3437</v>
+        <v>24.8929</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.273</v>
+        <v>0.2832</v>
       </c>
       <c r="J9" t="n">
-        <v>6.279</v>
+        <v>6.5136</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2837</v>
+        <v>-0.2685</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.5251</v>
+        <v>-6.1755</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4894</v>
+        <v>-0.4584</v>
       </c>
       <c r="J11" t="n">
-        <v>-11.2562</v>
+        <v>-10.5432</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3859</v>
+        <v>0.3801</v>
       </c>
       <c r="J12" t="n">
-        <v>10.8052</v>
+        <v>10.6428</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3467</v>
+        <v>0.3433</v>
       </c>
       <c r="J13" t="n">
-        <v>9.707599999999999</v>
+        <v>9.612399999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08</v>
+        <v>0.0834</v>
       </c>
       <c r="J14" t="n">
-        <v>2.24</v>
+        <v>2.3352</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3189</v>
+        <v>-0.3323</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.9292</v>
+        <v>-9.304399999999999</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.385</v>
+        <v>-0.3961</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.78</v>
+        <v>-11.0908</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0685</v>
+        <v>1.0323</v>
       </c>
       <c r="J17" t="n">
-        <v>29.918</v>
+        <v>28.9044</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.539</v>
+        <v>0.5255</v>
       </c>
       <c r="J18" t="n">
-        <v>15.092</v>
+        <v>14.714</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3072</v>
+        <v>0.3134</v>
       </c>
       <c r="J19" t="n">
-        <v>8.601599999999999</v>
+        <v>8.7752</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3072</v>
+        <v>0.3134</v>
       </c>
       <c r="J20" t="n">
-        <v>8.601599999999999</v>
+        <v>8.7752</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2198</v>
+        <v>0.232</v>
       </c>
       <c r="J21" t="n">
-        <v>6.1544</v>
+        <v>6.496</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.88</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3458</v>
+        <v>1.4608</v>
       </c>
       <c r="J22" t="n">
-        <v>37.6824</v>
+        <v>40.9024</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4266</v>
+        <v>0.4705</v>
       </c>
       <c r="J23" t="n">
-        <v>11.9448</v>
+        <v>13.174</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0436</v>
+        <v>-0.03</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.2208</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1769</v>
+        <v>-0.168</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.9532</v>
+        <v>-4.704</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4555</v>
+        <v>-0.4288</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.754</v>
+        <v>-12.0064</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.6367</v>
       </c>
       <c r="J27" t="n">
-        <v>16.0188</v>
+        <v>17.8276</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1622</v>
+        <v>0.1704</v>
       </c>
       <c r="J28" t="n">
-        <v>4.5416</v>
+        <v>4.7712</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.0989</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.4612</v>
+        <v>-2.7692</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1666</v>
+        <v>-0.18</v>
       </c>
       <c r="J30" t="n">
-        <v>-4.6648</v>
+        <v>-5.04</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2881</v>
+        <v>-0.3008</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.066800000000001</v>
+        <v>-8.4224</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5427</v>
+        <v>0.6006</v>
       </c>
       <c r="J32" t="n">
-        <v>13.5675</v>
+        <v>15.015</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5002</v>
+        <v>0.5533</v>
       </c>
       <c r="J33" t="n">
-        <v>12.505</v>
+        <v>13.8325</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3993</v>
+        <v>0.436</v>
       </c>
       <c r="J34" t="n">
-        <v>9.9825</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2838</v>
+        <v>0.2906</v>
       </c>
       <c r="J35" t="n">
-        <v>7.095</v>
+        <v>7.265</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.08</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2548</v>
+        <v>0.2636</v>
       </c>
       <c r="J36" t="n">
-        <v>6.37</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2874</v>
+        <v>0.2824</v>
       </c>
       <c r="J37" t="n">
-        <v>7.185</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.06</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1986</v>
+        <v>0.1969</v>
       </c>
       <c r="J38" t="n">
-        <v>4.965</v>
+        <v>4.9225</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1937</v>
+        <v>-0.2106</v>
       </c>
       <c r="J39" t="n">
-        <v>-4.8425</v>
+        <v>-5.265</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3303</v>
+        <v>-0.3447</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.2575</v>
+        <v>-8.6175</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3303</v>
+        <v>-0.3447</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.2575</v>
+        <v>-8.6175</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4963</v>
+        <v>0.5462</v>
       </c>
       <c r="J42" t="n">
-        <v>13.4001</v>
+        <v>14.7474</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3428</v>
+        <v>0.3496</v>
       </c>
       <c r="J43" t="n">
-        <v>9.255599999999999</v>
+        <v>9.4392</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2964</v>
+        <v>0.2992</v>
       </c>
       <c r="J44" t="n">
-        <v>8.002800000000001</v>
+        <v>8.0784</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1449</v>
+        <v>0.1556</v>
       </c>
       <c r="J45" t="n">
-        <v>3.9123</v>
+        <v>4.2012</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1105</v>
+        <v>0.1222</v>
       </c>
       <c r="J46" t="n">
-        <v>2.9835</v>
+        <v>3.2994</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2835</v>
+        <v>0.2841</v>
       </c>
       <c r="J47" t="n">
-        <v>7.6545</v>
+        <v>7.6707</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2628</v>
+        <v>0.2644</v>
       </c>
       <c r="J48" t="n">
-        <v>7.0956</v>
+        <v>7.1388</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1532</v>
+        <v>0.1579</v>
       </c>
       <c r="J49" t="n">
-        <v>4.1364</v>
+        <v>4.2633</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1812</v>
+        <v>-0.1962</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.8924</v>
+        <v>-5.2974</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4229</v>
+        <v>-0.4323</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.4183</v>
+        <v>-11.6721</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1203</v>
+        <v>0.1259</v>
       </c>
       <c r="J52" t="n">
-        <v>3.4887</v>
+        <v>3.6511</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0102</v>
+        <v>0.0074</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2958</v>
+        <v>0.2146</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0102</v>
+        <v>0.0074</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2958</v>
+        <v>0.2146</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1691</v>
+        <v>-0.1845</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.9039</v>
+        <v>-5.3505</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.299</v>
+        <v>-0.3131</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.670999999999999</v>
+        <v>-9.0799</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.54</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5298</v>
+        <v>0.606</v>
       </c>
       <c r="J57" t="n">
-        <v>15.3642</v>
+        <v>17.574</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4783</v>
+        <v>0.5457</v>
       </c>
       <c r="J58" t="n">
-        <v>13.8707</v>
+        <v>15.8253</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3438</v>
+        <v>0.3678</v>
       </c>
       <c r="J59" t="n">
-        <v>9.9702</v>
+        <v>10.6662</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0233</v>
+        <v>0.0367</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6757</v>
+        <v>1.0643</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3184</v>
+        <v>-0.3265</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.233599999999999</v>
+        <v>-9.468500000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.29</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6132</v>
+        <v>0.6754</v>
       </c>
       <c r="J62" t="n">
-        <v>24.528</v>
+        <v>27.016</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4531</v>
+        <v>0.4974</v>
       </c>
       <c r="J63" t="n">
-        <v>18.124</v>
+        <v>19.896</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.13</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3764</v>
+        <v>0.4</v>
       </c>
       <c r="J64" t="n">
-        <v>15.056</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.323</v>
+        <v>0.3254</v>
       </c>
       <c r="J65" t="n">
-        <v>12.92</v>
+        <v>13.016</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7991</v>
+        <v>-0.7398</v>
       </c>
       <c r="J66" t="n">
-        <v>-31.964</v>
+        <v>-29.592</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4486</v>
+        <v>0.4962</v>
       </c>
       <c r="J67" t="n">
-        <v>17.944</v>
+        <v>19.848</v>
       </c>
     </row>
     <row r="68">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0361</v>
+        <v>-0.0428</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.444</v>
+        <v>-1.712</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1345</v>
+        <v>-0.1471</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.38</v>
+        <v>-5.884</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1564</v>
+        <v>-0.1695</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.256</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9791</v>
+        <v>0.9319</v>
       </c>
       <c r="J72" t="n">
-        <v>29.373</v>
+        <v>27.957</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.22</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4555</v>
+        <v>0.4531</v>
       </c>
       <c r="J73" t="n">
-        <v>13.665</v>
+        <v>13.593</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2522</v>
+        <v>0.2615</v>
       </c>
       <c r="J74" t="n">
-        <v>7.566</v>
+        <v>7.845</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2956</v>
+        <v>-0.3067</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.868</v>
+        <v>-9.201000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3339</v>
+        <v>-0.3441</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.017</v>
+        <v>-10.323</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6872</v>
+        <v>0.6525</v>
       </c>
       <c r="J77" t="n">
-        <v>20.616</v>
+        <v>19.575</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4592</v>
+        <v>0.4486</v>
       </c>
       <c r="J78" t="n">
-        <v>13.776</v>
+        <v>13.458</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.211</v>
+        <v>0.2182</v>
       </c>
       <c r="J79" t="n">
-        <v>6.33</v>
+        <v>6.546</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1129</v>
+        <v>0.1238</v>
       </c>
       <c r="J80" t="n">
-        <v>3.387</v>
+        <v>3.714</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2204</v>
+        <v>-0.2163</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.612</v>
+        <v>-6.489</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.11</v>
       </c>
       <c r="I82" t="n">
-        <v>0.307</v>
+        <v>0.3014</v>
       </c>
       <c r="J82" t="n">
-        <v>7.675</v>
+        <v>7.535</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.89</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.1333</v>
+        <v>-0.149</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.3325</v>
+        <v>-3.725</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1841</v>
+        <v>-0.2009</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.6025</v>
+        <v>-5.0225</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1942</v>
+        <v>-0.211</v>
       </c>
       <c r="J85" t="n">
-        <v>-4.855</v>
+        <v>-5.275</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3022</v>
+        <v>-0.3174</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.555</v>
+        <v>-7.935</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1263</v>
+        <v>1.0884</v>
       </c>
       <c r="J87" t="n">
-        <v>28.1575</v>
+        <v>27.21</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.8137</v>
+        <v>0.7712</v>
       </c>
       <c r="J88" t="n">
-        <v>20.3425</v>
+        <v>19.28</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.7217</v>
+        <v>0.6901</v>
       </c>
       <c r="J89" t="n">
-        <v>18.0425</v>
+        <v>17.2525</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3555</v>
+        <v>0.3596</v>
       </c>
       <c r="J90" t="n">
-        <v>8.887499999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.5184</v>
+        <v>-0.4844</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.96</v>
+        <v>-12.11</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.13</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3119</v>
+        <v>0.3137</v>
       </c>
       <c r="J92" t="n">
-        <v>13.0998</v>
+        <v>13.1754</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1436</v>
+        <v>0.151</v>
       </c>
       <c r="J93" t="n">
-        <v>6.0312</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.03</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0956</v>
+        <v>0.1027</v>
       </c>
       <c r="J94" t="n">
-        <v>4.0152</v>
+        <v>4.3134</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1209</v>
+        <v>-0.1337</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.0778</v>
+        <v>-5.6154</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2566</v>
+        <v>-0.2702</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.7772</v>
+        <v>-11.3484</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2727</v>
+        <v>1.2391</v>
       </c>
       <c r="J97" t="n">
-        <v>53.4534</v>
+        <v>52.0422</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4022</v>
+        <v>0.3976</v>
       </c>
       <c r="J98" t="n">
-        <v>16.8924</v>
+        <v>16.6992</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0761</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.3054</v>
+        <v>-3.1962</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3192</v>
+        <v>-0.3079</v>
       </c>
       <c r="J100" t="n">
-        <v>-13.4064</v>
+        <v>-12.9318</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3783</v>
+        <v>-0.3625</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.8886</v>
+        <v>-15.225</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.87</v>
       </c>
       <c r="I102" t="n">
-        <v>1.0024</v>
+        <v>0.9813</v>
       </c>
       <c r="J102" t="n">
-        <v>29.0696</v>
+        <v>28.4577</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2202</v>
+        <v>0.2382</v>
       </c>
       <c r="J103" t="n">
-        <v>6.3858</v>
+        <v>6.9078</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.043</v>
+        <v>0.0575</v>
       </c>
       <c r="J104" t="n">
-        <v>1.247</v>
+        <v>1.6675</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0553</v>
+        <v>-0.0577</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.6037</v>
+        <v>-1.6733</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.096</v>
+        <v>-0.1017</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.784</v>
+        <v>-2.9493</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3896</v>
+        <v>0.3831</v>
       </c>
       <c r="J107" t="n">
-        <v>11.2984</v>
+        <v>11.1099</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0756</v>
+        <v>-0.0895</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.1924</v>
+        <v>-2.5955</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2234</v>
+        <v>-0.2403</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.4786</v>
+        <v>-6.9687</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2917</v>
+        <v>-0.3074</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.459300000000001</v>
+        <v>-8.9146</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3395</v>
+        <v>-0.3537</v>
       </c>
       <c r="J111" t="n">
-        <v>-9.845499999999999</v>
+        <v>-10.2573</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4678</v>
+        <v>0.4406</v>
       </c>
       <c r="J112" t="n">
-        <v>12.1628</v>
+        <v>11.4556</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.93</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0876</v>
       </c>
       <c r="J113" t="n">
-        <v>-1.7966</v>
+        <v>-2.2776</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.71</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2968</v>
+        <v>-0.3151</v>
       </c>
       <c r="J114" t="n">
-        <v>-7.7168</v>
+        <v>-8.192600000000001</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4562</v>
+        <v>-0.4674</v>
       </c>
       <c r="J115" t="n">
-        <v>-11.8612</v>
+        <v>-12.1524</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4841</v>
+        <v>-0.4936</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.5866</v>
+        <v>-12.8336</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.573</v>
+        <v>1.563</v>
       </c>
       <c r="J117" t="n">
-        <v>40.898</v>
+        <v>40.638</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8952</v>
+        <v>0.8442</v>
       </c>
       <c r="J118" t="n">
-        <v>23.2752</v>
+        <v>21.9492</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5535</v>
+        <v>0.5407</v>
       </c>
       <c r="J119" t="n">
-        <v>14.391</v>
+        <v>14.0582</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4018</v>
+        <v>0.4035</v>
       </c>
       <c r="J120" t="n">
-        <v>10.4468</v>
+        <v>10.491</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-1.0291</v>
+        <v>-0.9345</v>
       </c>
       <c r="J121" t="n">
-        <v>-26.7566</v>
+        <v>-24.297</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5202</v>
+        <v>0.4938</v>
       </c>
       <c r="J122" t="n">
-        <v>11.4444</v>
+        <v>10.8636</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.198</v>
+        <v>-0.2163</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.356</v>
+        <v>-4.7586</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2554</v>
+        <v>-0.2733</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.6188</v>
+        <v>-6.0126</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2842</v>
+        <v>-0.3015</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.2524</v>
+        <v>-6.633</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4349</v>
+        <v>-0.4462</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.5678</v>
+        <v>-9.8164</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.613</v>
+        <v>1.6114</v>
       </c>
       <c r="J127" t="n">
-        <v>35.486</v>
+        <v>35.4508</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.69</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3342</v>
+        <v>1.3176</v>
       </c>
       <c r="J128" t="n">
-        <v>29.3524</v>
+        <v>28.9872</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6486</v>
       </c>
       <c r="J129" t="n">
-        <v>14.6916</v>
+        <v>14.2692</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5728</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>12.6016</v>
+        <v>12.408</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6882</v>
+        <v>-0.6298</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.1404</v>
+        <v>-13.8556</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.08</v>
       </c>
       <c r="I132" t="n">
-        <v>0.228</v>
+        <v>0.2292</v>
       </c>
       <c r="J132" t="n">
-        <v>6.612</v>
+        <v>6.6468</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0549</v>
+        <v>0.0557</v>
       </c>
       <c r="J133" t="n">
-        <v>1.5921</v>
+        <v>1.6153</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.3548</v>
+        <v>-2.7202</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1989</v>
+        <v>-0.2146</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.7681</v>
+        <v>-6.2234</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.2977</v>
+        <v>-0.3121</v>
       </c>
       <c r="J136" t="n">
-        <v>-8.6333</v>
+        <v>-9.0509</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.1172</v>
+        <v>1.0778</v>
       </c>
       <c r="J137" t="n">
-        <v>32.3988</v>
+        <v>31.2562</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.25</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.6513</v>
       </c>
       <c r="J138" t="n">
-        <v>19.6881</v>
+        <v>18.8877</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.15</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4383</v>
+        <v>0.4344</v>
       </c>
       <c r="J139" t="n">
-        <v>12.7107</v>
+        <v>12.5976</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2463</v>
+        <v>0.2577</v>
       </c>
       <c r="J140" t="n">
-        <v>7.1427</v>
+        <v>7.4733</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.01</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0078</v>
+        <v>0.0273</v>
       </c>
       <c r="J141" t="n">
-        <v>0.2262</v>
+        <v>0.7917</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.77</v>
       </c>
       <c r="I142" t="n">
-        <v>1.437</v>
+        <v>1.4249</v>
       </c>
       <c r="J142" t="n">
-        <v>31.614</v>
+        <v>31.3478</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.59</v>
       </c>
       <c r="I143" t="n">
-        <v>1.2222</v>
+        <v>1.1967</v>
       </c>
       <c r="J143" t="n">
-        <v>26.8884</v>
+        <v>26.3274</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4822</v>
+        <v>0.4811</v>
       </c>
       <c r="J144" t="n">
-        <v>10.6084</v>
+        <v>10.5842</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.269</v>
+        <v>0.2869</v>
       </c>
       <c r="J145" t="n">
-        <v>5.918</v>
+        <v>6.3118</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.08</v>
       </c>
       <c r="I146" t="n">
-        <v>0.211</v>
+        <v>0.2331</v>
       </c>
       <c r="J146" t="n">
-        <v>4.642</v>
+        <v>5.1282</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3405</v>
+        <v>0.317</v>
       </c>
       <c r="J147" t="n">
-        <v>7.491</v>
+        <v>6.974</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.77</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2365</v>
+        <v>-0.2568</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.203</v>
+        <v>-5.6496</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.75</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2556</v>
+        <v>-0.2756</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.6232</v>
+        <v>-6.0632</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3103</v>
+        <v>-0.3292</v>
       </c>
       <c r="J150" t="n">
-        <v>-6.8266</v>
+        <v>-7.2424</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6175</v>
+        <v>-0.6188</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.585</v>
+        <v>-13.6136</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.14</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2849</v>
+        <v>0.2837</v>
       </c>
       <c r="J152" t="n">
-        <v>7.6923</v>
+        <v>7.6599</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-0.0892</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.0331</v>
+        <v>-2.4084</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1106</v>
+        <v>-0.1259</v>
       </c>
       <c r="J154" t="n">
-        <v>-2.9862</v>
+        <v>-3.3993</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2132</v>
+        <v>-0.2302</v>
       </c>
       <c r="J155" t="n">
-        <v>-5.7564</v>
+        <v>-6.2154</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4604</v>
+        <v>-0.4692</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.4308</v>
+        <v>-12.6684</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6925</v>
+        <v>0.6903</v>
       </c>
       <c r="J157" t="n">
-        <v>18.6975</v>
+        <v>18.6381</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3949</v>
+        <v>0.41</v>
       </c>
       <c r="J158" t="n">
-        <v>10.6623</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3031</v>
+        <v>0.3208</v>
       </c>
       <c r="J159" t="n">
-        <v>8.1837</v>
+        <v>8.6616</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.056</v>
+        <v>0.0726</v>
       </c>
       <c r="J160" t="n">
-        <v>1.512</v>
+        <v>1.9602</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0385</v>
+        <v>0.0541</v>
       </c>
       <c r="J161" t="n">
-        <v>1.0395</v>
+        <v>1.4607</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3491</v>
+        <v>1.3286</v>
       </c>
       <c r="J162" t="n">
-        <v>37.7748</v>
+        <v>37.2008</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1015</v>
+        <v>1.0636</v>
       </c>
       <c r="J163" t="n">
-        <v>30.842</v>
+        <v>29.7808</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3426</v>
+        <v>0.3506</v>
       </c>
       <c r="J164" t="n">
-        <v>9.5928</v>
+        <v>9.816800000000001</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.03</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0683</v>
+        <v>0.0929</v>
       </c>
       <c r="J165" t="n">
-        <v>1.9124</v>
+        <v>2.6012</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0312</v>
+        <v>0.0564</v>
       </c>
       <c r="J166" t="n">
-        <v>0.8736</v>
+        <v>1.5792</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8517</v>
+        <v>0.8012</v>
       </c>
       <c r="J167" t="n">
-        <v>23.8476</v>
+        <v>22.4336</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0185</v>
+        <v>0.0133</v>
       </c>
       <c r="J168" t="n">
-        <v>0.518</v>
+        <v>0.3724</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1875</v>
+        <v>-0.2035</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.25</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2477</v>
+        <v>-0.2633</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.9356</v>
+        <v>-7.3724</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5013</v>
+        <v>-0.5072</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.0364</v>
+        <v>-14.2016</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.7569</v>
+        <v>0.701</v>
       </c>
       <c r="J172" t="n">
-        <v>15.8949</v>
+        <v>14.721</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2489</v>
+        <v>-0.2684</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.2269</v>
+        <v>-5.6364</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2669</v>
+        <v>-0.2863</v>
       </c>
       <c r="J174" t="n">
-        <v>-5.6049</v>
+        <v>-6.0123</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3137</v>
+        <v>-0.3318</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.5877</v>
+        <v>-6.9678</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6844</v>
+        <v>-0.6801</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.3724</v>
+        <v>-14.2821</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.07</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7509</v>
+        <v>1.7583</v>
       </c>
       <c r="J177" t="n">
-        <v>36.7689</v>
+        <v>36.9243</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.83</v>
       </c>
       <c r="I178" t="n">
-        <v>1.4811</v>
+        <v>1.4757</v>
       </c>
       <c r="J178" t="n">
-        <v>31.1031</v>
+        <v>30.9897</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.45</v>
       </c>
       <c r="I179" t="n">
-        <v>1.0374</v>
+        <v>0.995</v>
       </c>
       <c r="J179" t="n">
-        <v>21.7854</v>
+        <v>20.895</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.7217</v>
+        <v>0.6992</v>
       </c>
       <c r="J180" t="n">
-        <v>15.1557</v>
+        <v>14.6832</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.65</v>
       </c>
       <c r="I181" t="n">
-        <v>-1.0896</v>
+        <v>-0.9811</v>
       </c>
       <c r="J181" t="n">
-        <v>-22.8816</v>
+        <v>-20.6031</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.09</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7674</v>
+        <v>1.7763</v>
       </c>
       <c r="J182" t="n">
-        <v>35.348</v>
+        <v>35.526</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.97</v>
       </c>
       <c r="I183" t="n">
-        <v>1.6342</v>
+        <v>1.6374</v>
       </c>
       <c r="J183" t="n">
-        <v>32.684</v>
+        <v>32.748</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5033</v>
+        <v>0.5059</v>
       </c>
       <c r="J184" t="n">
-        <v>10.066</v>
+        <v>10.118</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.11</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2681</v>
+        <v>0.2925</v>
       </c>
       <c r="J185" t="n">
-        <v>5.362</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0217</v>
+        <v>0.0601</v>
       </c>
       <c r="J186" t="n">
-        <v>0.434</v>
+        <v>1.202</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.2161</v>
+        <v>0.1979</v>
       </c>
       <c r="J187" t="n">
-        <v>4.322</v>
+        <v>3.958</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1545</v>
+        <v>-0.1757</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.09</v>
+        <v>-3.514</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2467</v>
+        <v>-0.2667</v>
       </c>
       <c r="J189" t="n">
-        <v>-4.934</v>
+        <v>-5.334</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3576</v>
+        <v>-0.3746</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.152</v>
+        <v>-7.492</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.39</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5903</v>
+        <v>-0.5935</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.806</v>
+        <v>-11.87</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.33</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6525</v>
+        <v>0.6322</v>
       </c>
       <c r="J192" t="n">
-        <v>15.0075</v>
+        <v>14.5406</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4971</v>
+        <v>0.4903</v>
       </c>
       <c r="J193" t="n">
-        <v>11.4333</v>
+        <v>11.2769</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2564</v>
+        <v>0.2645</v>
       </c>
       <c r="J194" t="n">
-        <v>5.8972</v>
+        <v>6.0835</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0034</v>
+        <v>-0.0026</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0598</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4877</v>
+        <v>-0.4923</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.2171</v>
+        <v>-11.3229</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8801</v>
+        <v>0.8297</v>
       </c>
       <c r="J197" t="n">
-        <v>20.2423</v>
+        <v>19.0831</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.31</v>
       </c>
       <c r="I198" t="n">
-        <v>0.8121</v>
+        <v>0.7701</v>
       </c>
       <c r="J198" t="n">
-        <v>18.6783</v>
+        <v>17.7123</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.6046</v>
+        <v>0.5859</v>
       </c>
       <c r="J199" t="n">
-        <v>13.9058</v>
+        <v>13.4757</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3542</v>
+        <v>0.3586</v>
       </c>
       <c r="J200" t="n">
-        <v>8.146599999999999</v>
+        <v>8.2478</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2702</v>
+        <v>0.2812</v>
       </c>
       <c r="J201" t="n">
-        <v>6.2146</v>
+        <v>6.4676</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7746</v>
+        <v>0.7269</v>
       </c>
       <c r="J202" t="n">
-        <v>32.5332</v>
+        <v>30.5298</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5739</v>
+        <v>0.5495</v>
       </c>
       <c r="J203" t="n">
-        <v>24.1038</v>
+        <v>23.079</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1205</v>
+        <v>0.129</v>
       </c>
       <c r="J204" t="n">
-        <v>5.061</v>
+        <v>5.418</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2111</v>
+        <v>-0.2099</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.866199999999999</v>
+        <v>-8.815799999999999</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.584</v>
+        <v>-0.5515</v>
       </c>
       <c r="J206" t="n">
-        <v>-24.528</v>
+        <v>-23.163</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4657</v>
+        <v>0.4605</v>
       </c>
       <c r="J207" t="n">
-        <v>19.5594</v>
+        <v>19.341</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.09</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2192</v>
+        <v>0.2279</v>
       </c>
       <c r="J208" t="n">
-        <v>9.2064</v>
+        <v>9.5718</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0343</v>
+        <v>0.0409</v>
       </c>
       <c r="J209" t="n">
-        <v>1.4406</v>
+        <v>1.7178</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.023</v>
+        <v>-0.0271</v>
       </c>
       <c r="J210" t="n">
-        <v>-0.966</v>
+        <v>-1.1382</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2018</v>
+        <v>-0.2146</v>
       </c>
       <c r="J211" t="n">
-        <v>-8.4756</v>
+        <v>-9.013199999999999</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4333</v>
+        <v>0.4112</v>
       </c>
       <c r="J212" t="n">
-        <v>9.099299999999999</v>
+        <v>8.635199999999999</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1853</v>
+        <v>0.1752</v>
       </c>
       <c r="J213" t="n">
-        <v>3.8913</v>
+        <v>3.6792</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.6</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.4036</v>
+        <v>-0.417</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.4756</v>
+        <v>-8.757</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4129</v>
+        <v>-0.4259</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.6709</v>
+        <v>-8.943899999999999</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.58</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4222</v>
+        <v>-0.4347</v>
       </c>
       <c r="J216" t="n">
-        <v>-8.866199999999999</v>
+        <v>-9.1287</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.82</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4988</v>
+        <v>1.4895</v>
       </c>
       <c r="J217" t="n">
-        <v>31.4748</v>
+        <v>31.2795</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0519</v>
+        <v>1.0084</v>
       </c>
       <c r="J218" t="n">
-        <v>22.0899</v>
+        <v>21.1764</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.7237</v>
+        <v>0.6962</v>
       </c>
       <c r="J219" t="n">
-        <v>15.1977</v>
+        <v>14.6202</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5347</v>
+        <v>0.5278</v>
       </c>
       <c r="J220" t="n">
-        <v>11.2287</v>
+        <v>11.0838</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.91</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.405</v>
+        <v>-0.3748</v>
       </c>
       <c r="J221" t="n">
-        <v>-8.505000000000001</v>
+        <v>-7.8708</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.31</v>
       </c>
       <c r="I222" t="n">
-        <v>0.6158</v>
+        <v>0.5994</v>
       </c>
       <c r="J222" t="n">
-        <v>17.2424</v>
+        <v>16.7832</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2548</v>
+        <v>0.2633</v>
       </c>
       <c r="J223" t="n">
-        <v>7.1344</v>
+        <v>7.3724</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0251</v>
+        <v>-0.0287</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.7028</v>
+        <v>-0.8036</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0408</v>
+        <v>-0.0464</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.1424</v>
+        <v>-1.2992</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.87</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1727</v>
+        <v>-0.1847</v>
       </c>
       <c r="J226" t="n">
-        <v>-4.8356</v>
+        <v>-5.1716</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7729</v>
+        <v>0.7257</v>
       </c>
       <c r="J227" t="n">
-        <v>21.6412</v>
+        <v>20.3196</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7236</v>
+        <v>0.6824</v>
       </c>
       <c r="J228" t="n">
-        <v>20.2608</v>
+        <v>19.1072</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1856</v>
+        <v>0.1924</v>
       </c>
       <c r="J229" t="n">
-        <v>5.1968</v>
+        <v>5.3872</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.179</v>
+        <v>-0.1788</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.012</v>
+        <v>-5.0064</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7654</v>
+        <v>-0.7117</v>
       </c>
       <c r="J231" t="n">
-        <v>-21.4312</v>
+        <v>-19.9276</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3427/event_3427_evp_summary.xlsx
+++ b/database/event/3427/event_3427_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.4492</v>
+        <v>5.5481</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5472</v>
+        <v>0.5571</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8564</v>
+        <v>1.9216</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4492</v>
+        <v>5.5481</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3021</v>
+        <v>2.4438</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1471</v>
+        <v>3.1043</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7012</v>
+        <v>2.7327</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4586</v>
+        <v>1.5343</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1471</v>
+        <v>3.1043</v>
       </c>
       <c r="K2" t="n">
         <v>48</v>
@@ -529,7 +529,7 @@
         <v>104</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6057</v>
+        <v>4.6386</v>
       </c>
       <c r="N2" t="n">
         <v>152</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.913</v>
+        <v>4.8487</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4933</v>
+        <v>0.4869</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6123</v>
+        <v>1.603</v>
       </c>
       <c r="E3" t="n">
-        <v>4.913</v>
+        <v>4.8487</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8634</v>
+        <v>2.8923</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0496</v>
+        <v>1.9564</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5532</v>
+        <v>4.4163</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4587</v>
+        <v>2.4796</v>
       </c>
       <c r="J3" t="n">
-        <v>2.0496</v>
+        <v>1.9564</v>
       </c>
       <c r="K3" t="n">
         <v>48</v>
@@ -575,7 +575,7 @@
         <v>104</v>
       </c>
       <c r="M3" t="n">
-        <v>4.5083</v>
+        <v>4.436</v>
       </c>
       <c r="N3" t="n">
         <v>152</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3783</v>
+        <v>4.2881</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4396</v>
+        <v>0.4306</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3689</v>
+        <v>1.3476</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3783</v>
+        <v>4.2881</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1746</v>
+        <v>2.0854</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2037</v>
+        <v>2.2027</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2808</v>
+        <v>2.0854</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2316</v>
+        <v>1.1709</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2037</v>
+        <v>2.2027</v>
       </c>
       <c r="K4" t="n">
         <v>48</v>
@@ -621,7 +621,7 @@
         <v>104</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4353</v>
+        <v>3.3736</v>
       </c>
       <c r="N4" t="n">
         <v>152</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.1605</v>
+        <v>4.0707</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4178</v>
+        <v>0.4088</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2697</v>
+        <v>1.2486</v>
       </c>
       <c r="E5" t="n">
-        <v>4.1605</v>
+        <v>4.0707</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2414</v>
+        <v>3.229</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9191</v>
+        <v>0.8417</v>
       </c>
       <c r="H5" t="n">
-        <v>5.8005</v>
+        <v>5.6803</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1322</v>
+        <v>3.1893</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9191</v>
+        <v>0.8417</v>
       </c>
       <c r="K5" t="n">
         <v>129</v>
@@ -667,7 +667,7 @@
         <v>53</v>
       </c>
       <c r="M5" t="n">
-        <v>4.0513</v>
+        <v>4.031</v>
       </c>
       <c r="N5" t="n">
         <v>182</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.0951</v>
+        <v>3.9942</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4112</v>
+        <v>0.4011</v>
       </c>
       <c r="D6" t="n">
-        <v>1.24</v>
+        <v>1.2138</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0951</v>
+        <v>3.9942</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2051</v>
+        <v>3.1913</v>
       </c>
       <c r="G6" t="n">
-        <v>0.89</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>5.6806</v>
+        <v>5.5389</v>
       </c>
       <c r="I6" t="n">
-        <v>3.0675</v>
+        <v>3.1099</v>
       </c>
       <c r="J6" t="n">
-        <v>0.89</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="K6" t="n">
         <v>202</v>
@@ -713,7 +713,7 @@
         <v>96</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9575</v>
+        <v>3.9128</v>
       </c>
       <c r="N6" t="n">
         <v>298</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.0931</v>
+        <v>3.9867</v>
       </c>
       <c r="C7" t="n">
-        <v>0.411</v>
+        <v>0.4003</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2391</v>
+        <v>1.2103</v>
       </c>
       <c r="E7" t="n">
-        <v>4.0931</v>
+        <v>3.9867</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0712</v>
+        <v>3.099</v>
       </c>
       <c r="G7" t="n">
-        <v>1.0219</v>
+        <v>0.8877</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2388</v>
+        <v>5.1923</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8289</v>
+        <v>2.9153</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0219</v>
+        <v>0.8877</v>
       </c>
       <c r="K7" t="n">
         <v>202</v>
@@ -759,7 +759,7 @@
         <v>96</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8508</v>
+        <v>3.803</v>
       </c>
       <c r="N7" t="n">
         <v>298</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9654</v>
+        <v>3.8878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3982</v>
+        <v>0.3904</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1809</v>
+        <v>1.1653</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9654</v>
+        <v>3.8878</v>
       </c>
       <c r="F8" t="n">
-        <v>2.936</v>
+        <v>2.9589</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0294</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7927</v>
+        <v>4.6665</v>
       </c>
       <c r="I8" t="n">
-        <v>2.588</v>
+        <v>2.6201</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0294</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>44</v>
@@ -805,7 +805,7 @@
         <v>147</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6174</v>
+        <v>3.549</v>
       </c>
       <c r="N8" t="n">
         <v>191</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6078</v>
+        <v>3.5463</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3623</v>
+        <v>0.3561</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0181</v>
+        <v>1.0097</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6078</v>
+        <v>3.5463</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3081</v>
+        <v>2.3919</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2997</v>
+        <v>1.1544</v>
       </c>
       <c r="H9" t="n">
-        <v>2.721</v>
+        <v>2.5375</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4693</v>
+        <v>1.4247</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2997</v>
+        <v>1.1544</v>
       </c>
       <c r="K9" t="n">
         <v>44</v>
@@ -851,7 +851,7 @@
         <v>147</v>
       </c>
       <c r="M9" t="n">
-        <v>2.769</v>
+        <v>2.5791</v>
       </c>
       <c r="N9" t="n">
         <v>191</v>
@@ -860,139 +860,139 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5388</v>
+        <v>3.5186</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3553</v>
+        <v>0.3533</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9867</v>
+        <v>0.9971</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5388</v>
+        <v>3.5186</v>
       </c>
       <c r="F10" t="n">
-        <v>3.2805</v>
+        <v>2.5485</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2583</v>
+        <v>0.9701</v>
       </c>
       <c r="H10" t="n">
-        <v>5.9294</v>
+        <v>3.1257</v>
       </c>
       <c r="I10" t="n">
-        <v>3.2018</v>
+        <v>1.755</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2583</v>
+        <v>0.9701</v>
       </c>
       <c r="K10" t="n">
-        <v>202</v>
+        <v>44</v>
       </c>
       <c r="L10" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4601</v>
+        <v>2.7251</v>
       </c>
       <c r="N10" t="n">
-        <v>298</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mou</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.5356</v>
+        <v>3.4463</v>
       </c>
       <c r="C11" t="n">
-        <v>0.355</v>
+        <v>0.3461</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9853</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>3.5356</v>
+        <v>3.4463</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6395</v>
+        <v>3.2378</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1039</v>
+        <v>0.2085</v>
       </c>
       <c r="H11" t="n">
-        <v>7.114</v>
+        <v>5.7134</v>
       </c>
       <c r="I11" t="n">
-        <v>3.8415</v>
+        <v>3.2079</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1039</v>
+        <v>0.2085</v>
       </c>
       <c r="K11" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L11" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M11" t="n">
-        <v>3.7376</v>
+        <v>3.4164</v>
       </c>
       <c r="N11" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>mou</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5178</v>
+        <v>3.3732</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3532</v>
+        <v>0.3387</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9772</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5178</v>
+        <v>3.3732</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4695</v>
+        <v>3.4993</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0483</v>
+        <v>-0.1261</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2536</v>
+        <v>6.6951</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7569</v>
+        <v>3.7591</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0483</v>
+        <v>-0.1261</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="L12" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="M12" t="n">
-        <v>2.8052</v>
+        <v>3.633</v>
       </c>
       <c r="N12" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.5015</v>
+        <v>2.5119</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2512</v>
+        <v>0.2522</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5145</v>
+        <v>0.5385</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5015</v>
+        <v>2.5119</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3707</v>
+        <v>2.4531</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1308</v>
+        <v>0.0588</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9276</v>
+        <v>2.7672</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5809</v>
+        <v>1.5537</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1308</v>
+        <v>0.0588</v>
       </c>
       <c r="K13" t="n">
         <v>44</v>
@@ -1035,7 +1035,7 @@
         <v>147</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7117</v>
+        <v>1.6125</v>
       </c>
       <c r="N13" t="n">
         <v>191</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.1592</v>
+        <v>2.176</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2168</v>
+        <v>0.2185</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3587</v>
+        <v>0.3855</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1592</v>
+        <v>2.176</v>
       </c>
       <c r="F14" t="n">
-        <v>2.3335</v>
+        <v>2.372</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1743</v>
+        <v>-0.196</v>
       </c>
       <c r="H14" t="n">
-        <v>2.805</v>
+        <v>2.463</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5147</v>
+        <v>1.3829</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1743</v>
+        <v>-0.196</v>
       </c>
       <c r="K14" t="n">
         <v>129</v>
@@ -1081,7 +1081,7 @@
         <v>53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.3404</v>
+        <v>1.1869</v>
       </c>
       <c r="N14" t="n">
         <v>182</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1829</v>
+        <v>0.1766</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2052</v>
+        <v>0.1954</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8219</v>
+        <v>1.7588</v>
       </c>
       <c r="N15" t="n">
         <v>97</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1763</v>
+        <v>0.1564</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1752</v>
+        <v>0.1039</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7561</v>
+        <v>1.5578</v>
       </c>
       <c r="N16" t="n">
         <v>119</v>
@@ -1182,185 +1182,185 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mir</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.5329</v>
+        <v>1.4866</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1539</v>
+        <v>0.1493</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0736</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5329</v>
+        <v>1.4866</v>
       </c>
       <c r="F17" t="n">
-        <v>2.0576</v>
+        <v>2.1241</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.6375</v>
       </c>
       <c r="H17" t="n">
-        <v>2.0576</v>
+        <v>2.1241</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1111</v>
+        <v>1.1926</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5247000000000001</v>
+        <v>-0.6375</v>
       </c>
       <c r="K17" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="L17" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5863999999999999</v>
+        <v>0.5551000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>182</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>mir</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.5087</v>
+        <v>1.2988</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1515</v>
+        <v>0.1304</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0626</v>
+        <v>-0.0141</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5087</v>
+        <v>1.2988</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2009</v>
+        <v>1.7875</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6922</v>
+        <v>-0.4887</v>
       </c>
       <c r="H18" t="n">
-        <v>2.3674</v>
+        <v>1.7875</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2784</v>
+        <v>1.0036</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6922</v>
+        <v>-0.4887</v>
       </c>
       <c r="K18" t="n">
-        <v>202</v>
+        <v>129</v>
       </c>
       <c r="L18" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5861999999999999</v>
+        <v>0.5149</v>
       </c>
       <c r="N18" t="n">
-        <v>298</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dosia</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3657</v>
+        <v>1.1936</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1371</v>
+        <v>0.1199</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0025</v>
+        <v>-0.062</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3657</v>
+        <v>1.1936</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6752</v>
+        <v>1.1936</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3095</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6752</v>
+        <v>1.1936</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9046</v>
+        <v>1.1936</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3095</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="L19" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5951</v>
+        <v>1.1936</v>
       </c>
       <c r="N19" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>Dosia</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.3408</v>
+        <v>1.1713</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1346</v>
+        <v>0.1176</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0138</v>
+        <v>-0.0722</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3408</v>
+        <v>1.1713</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3408</v>
+        <v>1.4448</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.2735</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3408</v>
+        <v>1.4448</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3408</v>
+        <v>0.8112</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-0.2735</v>
       </c>
       <c r="K20" t="n">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="M20" t="n">
-        <v>1.3408</v>
+        <v>0.5377000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>159</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21">
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2422</v>
+        <v>1.0972</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1247</v>
+        <v>0.1102</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0587</v>
+        <v>-0.106</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2422</v>
+        <v>1.0972</v>
       </c>
       <c r="F21" t="n">
-        <v>0.898</v>
+        <v>0.7484</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3442</v>
+        <v>0.3488</v>
       </c>
       <c r="H21" t="n">
-        <v>0.898</v>
+        <v>0.7484</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4849</v>
+        <v>0.4202</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3442</v>
+        <v>0.3488</v>
       </c>
       <c r="K21" t="n">
         <v>48</v>
@@ -1403,7 +1403,7 @@
         <v>104</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.769</v>
       </c>
       <c r="N21" t="n">
         <v>152</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0732</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3292</v>
+        <v>-0.2735</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6481</v>
+        <v>0.7294</v>
       </c>
       <c r="N22" t="n">
         <v>97</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0426</v>
+        <v>0.0349</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4311</v>
+        <v>-0.4475</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4241</v>
+        <v>0.3475</v>
       </c>
       <c r="N23" t="n">
         <v>72</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0361</v>
+        <v>0.032</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4607</v>
+        <v>-0.4605</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.3591</v>
+        <v>0.319</v>
       </c>
       <c r="N24" t="n">
         <v>97</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0358</v>
+        <v>0.0291</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4617</v>
+        <v>-0.4738</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3569</v>
+        <v>0.2897</v>
       </c>
       <c r="N25" t="n">
         <v>72</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0272</v>
+        <v>0.0201</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5009</v>
+        <v>-0.5145</v>
       </c>
       <c r="E26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2708</v>
+        <v>0.2005</v>
       </c>
       <c r="N26" t="n">
         <v>119</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="C27" t="n">
-        <v>0.016</v>
+        <v>0.0137</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5516</v>
+        <v>-0.5436</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1595</v>
+        <v>0.1365</v>
       </c>
       <c r="N27" t="n">
         <v>159</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0111</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.5554</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0878</v>
+        <v>0.1105</v>
       </c>
       <c r="N28" t="n">
         <v>97</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>freddieb</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0017</v>
+        <v>-0.0075</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6318</v>
+        <v>-0.6399</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0166</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>freddieb</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0057</v>
+        <v>-0.0117</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6502</v>
+        <v>-0.6587</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.057</v>
+        <v>-0.1162</v>
       </c>
       <c r="N30" t="n">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0469</v>
+        <v>-0.0488</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.837</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4674</v>
+        <v>-0.4858</v>
       </c>
       <c r="N31" t="n">
         <v>159</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0472</v>
+        <v>-0.0505</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8383</v>
+        <v>-0.8348</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.4703</v>
+        <v>-0.5027</v>
       </c>
       <c r="N32" t="n">
         <v>119</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0585</v>
+        <v>-0.0572</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8895</v>
+        <v>-0.8653</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5827</v>
+        <v>-0.5696</v>
       </c>
       <c r="N33" t="n">
         <v>159</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0664</v>
+        <v>-0.0693</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.925</v>
+        <v>-0.9201</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.6899</v>
       </c>
       <c r="N34" t="n">
         <v>159</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9811</v>
+        <v>-0.9435</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7841</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.079</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9825</v>
+        <v>-0.9762999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7871</v>
+        <v>-0.8133</v>
       </c>
       <c r="N36" t="n">
         <v>119</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0829</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9999</v>
+        <v>-0.9828</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8252</v>
+        <v>-0.8275</v>
       </c>
       <c r="N37" t="n">
         <v>72</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0946</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.053</v>
+        <v>-1.0137</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8954</v>
       </c>
       <c r="N38" t="n">
         <v>72</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0373</v>
+        <v>-0.9415</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1042</v>
+        <v>-0.0945</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0964</v>
+        <v>-1.0347</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0373</v>
+        <v>-0.9415</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2067</v>
+        <v>-1.1482</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1694</v>
+        <v>0.2067</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2067</v>
+        <v>-1.1482</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6516</v>
+        <v>-0.6447000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1694</v>
+        <v>0.2067</v>
       </c>
       <c r="K39" t="n">
         <v>48</v>
@@ -2231,7 +2231,7 @@
         <v>104</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.4822</v>
+        <v>-0.4380000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>152</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.2382</v>
+        <v>-2.2605</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2247</v>
+        <v>-0.227</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.6431</v>
+        <v>-1.6356</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.2382</v>
+        <v>-2.2605</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2045</v>
+        <v>-2.2172</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0337</v>
+        <v>-0.0433</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2045</v>
+        <v>-2.2172</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.1904</v>
+        <v>-1.2449</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0337</v>
+        <v>-0.0433</v>
       </c>
       <c r="K40" t="n">
         <v>202</v>
@@ -2277,7 +2277,7 @@
         <v>96</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2241</v>
+        <v>-1.2882</v>
       </c>
       <c r="N40" t="n">
         <v>298</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.7424</v>
+        <v>-2.728</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2754</v>
+        <v>-0.2739</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8726</v>
+        <v>-1.8485</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7424</v>
+        <v>-2.728</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1528</v>
+        <v>-1.181</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.5896</v>
+        <v>-1.547</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1528</v>
+        <v>-1.181</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6225000000000001</v>
+        <v>-0.6631</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.5896</v>
+        <v>-1.547</v>
       </c>
       <c r="K41" t="n">
         <v>44</v>
@@ -2323,7 +2323,7 @@
         <v>147</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2121</v>
+        <v>-2.2101</v>
       </c>
       <c r="N41" t="n">
         <v>191</v>
@@ -2429,10 +2429,10 @@
         <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3642</v>
+        <v>0.3125</v>
       </c>
       <c r="J2" t="n">
-        <v>8.3766</v>
+        <v>7.1875</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1524</v>
+        <v>0.1181</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5052</v>
+        <v>2.7163</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.9</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1368</v>
+        <v>-0.1204</v>
       </c>
       <c r="J4" t="n">
-        <v>-3.1464</v>
+        <v>-2.7692</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.64</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3891</v>
+        <v>-0.3768</v>
       </c>
       <c r="J5" t="n">
-        <v>-8.949299999999999</v>
+        <v>-8.666399999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.6</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4248</v>
+        <v>-0.4158</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.7704</v>
+        <v>-9.5634</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.65</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4102</v>
+        <v>1.447</v>
       </c>
       <c r="J7" t="n">
-        <v>32.4346</v>
+        <v>33.281</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.47</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0823</v>
+        <v>1.0831</v>
       </c>
       <c r="J8" t="n">
-        <v>24.8929</v>
+        <v>24.9113</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2832</v>
+        <v>0.2513</v>
       </c>
       <c r="J9" t="n">
-        <v>6.5136</v>
+        <v>5.7799</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2685</v>
+        <v>-0.2303</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.1755</v>
+        <v>-5.2969</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4584</v>
+        <v>-0.418</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.5432</v>
+        <v>-9.614000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.16</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3801</v>
+        <v>0.3253</v>
       </c>
       <c r="J12" t="n">
-        <v>10.6428</v>
+        <v>9.1084</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.14</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3433</v>
+        <v>0.2902</v>
       </c>
       <c r="J13" t="n">
-        <v>9.612399999999999</v>
+        <v>8.1256</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0834</v>
+        <v>0.0595</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3352</v>
+        <v>1.666</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.71</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3323</v>
+        <v>-0.316</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.304399999999999</v>
+        <v>-8.848000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3961</v>
+        <v>-0.3848</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.0908</v>
+        <v>-10.7744</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.44</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0323</v>
+        <v>1.0274</v>
       </c>
       <c r="J17" t="n">
-        <v>28.9044</v>
+        <v>28.7672</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5255</v>
+        <v>0.4901</v>
       </c>
       <c r="J18" t="n">
-        <v>14.714</v>
+        <v>13.7228</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.1</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3134</v>
+        <v>0.2801</v>
       </c>
       <c r="J19" t="n">
-        <v>8.7752</v>
+        <v>7.8428</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.1</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3134</v>
+        <v>0.2801</v>
       </c>
       <c r="J20" t="n">
-        <v>8.7752</v>
+        <v>7.8428</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>1.07</v>
       </c>
       <c r="I21" t="n">
-        <v>0.232</v>
+        <v>0.2019</v>
       </c>
       <c r="J21" t="n">
-        <v>6.496</v>
+        <v>5.6532</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.88</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4608</v>
+        <v>1.4837</v>
       </c>
       <c r="J22" t="n">
-        <v>40.9024</v>
+        <v>41.5436</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.17</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4705</v>
+        <v>0.4462</v>
       </c>
       <c r="J23" t="n">
-        <v>13.174</v>
+        <v>12.4936</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.03</v>
+        <v>-0.0245</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.84</v>
+        <v>-0.6860000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.97</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.168</v>
+        <v>-0.1365</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.704</v>
+        <v>-3.822</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.88</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4288</v>
+        <v>-0.3875</v>
       </c>
       <c r="J26" t="n">
-        <v>-12.0064</v>
+        <v>-10.85</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6367</v>
+        <v>0.6071</v>
       </c>
       <c r="J27" t="n">
-        <v>17.8276</v>
+        <v>16.9988</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.06</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1704</v>
+        <v>0.1332</v>
       </c>
       <c r="J28" t="n">
-        <v>4.7712</v>
+        <v>3.7296</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0989</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.7692</v>
+        <v>-2.2988</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.87</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.18</v>
+        <v>-0.1595</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.04</v>
+        <v>-4.466</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.75</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3008</v>
+        <v>-0.2829</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.4224</v>
+        <v>-7.9212</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6006</v>
+        <v>0.5894</v>
       </c>
       <c r="J32" t="n">
-        <v>15.015</v>
+        <v>14.735</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5533</v>
+        <v>0.5444</v>
       </c>
       <c r="J33" t="n">
-        <v>13.8325</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.15</v>
       </c>
       <c r="I34" t="n">
-        <v>0.436</v>
+        <v>0.4021</v>
       </c>
       <c r="J34" t="n">
-        <v>10.9</v>
+        <v>10.0525</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.09</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2906</v>
+        <v>0.2574</v>
       </c>
       <c r="J35" t="n">
-        <v>7.265</v>
+        <v>6.435</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.08</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2636</v>
+        <v>0.2315</v>
       </c>
       <c r="J36" t="n">
-        <v>6.59</v>
+        <v>5.7875</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2824</v>
+        <v>0.2346</v>
       </c>
       <c r="J37" t="n">
-        <v>7.06</v>
+        <v>5.865</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.06</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1969</v>
+        <v>0.1568</v>
       </c>
       <c r="J38" t="n">
-        <v>4.9225</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.83</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2106</v>
+        <v>-0.1914</v>
       </c>
       <c r="J39" t="n">
-        <v>-5.265</v>
+        <v>-4.785</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3447</v>
+        <v>-0.3292</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.6175</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3447</v>
+        <v>-0.3292</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.6175</v>
+        <v>-8.23</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.21</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5462</v>
+        <v>0.5355</v>
       </c>
       <c r="J42" t="n">
-        <v>14.7474</v>
+        <v>14.4585</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.11</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3496</v>
+        <v>0.3115</v>
       </c>
       <c r="J43" t="n">
-        <v>9.4392</v>
+        <v>8.410500000000001</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2992</v>
+        <v>0.263</v>
       </c>
       <c r="J44" t="n">
-        <v>8.0784</v>
+        <v>7.101</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>1.04</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1556</v>
+        <v>0.1294</v>
       </c>
       <c r="J45" t="n">
-        <v>4.2012</v>
+        <v>3.4938</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>1.03</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1222</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="J46" t="n">
-        <v>3.2994</v>
+        <v>2.6892</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.11</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2841</v>
+        <v>0.2347</v>
       </c>
       <c r="J47" t="n">
-        <v>7.6707</v>
+        <v>6.3369</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2644</v>
+        <v>0.2165</v>
       </c>
       <c r="J48" t="n">
-        <v>7.1388</v>
+        <v>5.8455</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.05</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1579</v>
+        <v>0.1216</v>
       </c>
       <c r="J49" t="n">
-        <v>4.2633</v>
+        <v>3.2832</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.85</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1962</v>
+        <v>-0.176</v>
       </c>
       <c r="J50" t="n">
-        <v>-5.2974</v>
+        <v>-4.752</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4323</v>
+        <v>-0.4248</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.6721</v>
+        <v>-11.4696</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.05</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1259</v>
+        <v>0.1092</v>
       </c>
       <c r="J52" t="n">
-        <v>3.6511</v>
+        <v>3.1668</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0074</v>
+        <v>0.0053</v>
       </c>
       <c r="J53" t="n">
-        <v>0.2146</v>
+        <v>0.1537</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0074</v>
+        <v>0.0053</v>
       </c>
       <c r="J54" t="n">
-        <v>0.2146</v>
+        <v>0.1537</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.86</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.1845</v>
+        <v>-0.1646</v>
       </c>
       <c r="J55" t="n">
-        <v>-5.3505</v>
+        <v>-4.7734</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.73</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3131</v>
+        <v>-0.2956</v>
       </c>
       <c r="J56" t="n">
-        <v>-9.0799</v>
+        <v>-8.5724</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.54</v>
       </c>
       <c r="I57" t="n">
-        <v>0.606</v>
+        <v>0.5682</v>
       </c>
       <c r="J57" t="n">
-        <v>17.574</v>
+        <v>16.4778</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.46</v>
       </c>
       <c r="I58" t="n">
-        <v>0.5457</v>
+        <v>0.509</v>
       </c>
       <c r="J58" t="n">
-        <v>15.8253</v>
+        <v>14.761</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3678</v>
+        <v>0.3087</v>
       </c>
       <c r="J59" t="n">
-        <v>10.6662</v>
+        <v>8.952299999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0367</v>
+        <v>0.0245</v>
       </c>
       <c r="J60" t="n">
-        <v>1.0643</v>
+        <v>0.7105</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3265</v>
+        <v>-0.3123</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.468500000000001</v>
+        <v>-9.056699999999999</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.29</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6754</v>
+        <v>0.6603</v>
       </c>
       <c r="J62" t="n">
-        <v>27.016</v>
+        <v>26.412</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.18</v>
       </c>
       <c r="I63" t="n">
-        <v>0.4974</v>
+        <v>0.4778</v>
       </c>
       <c r="J63" t="n">
-        <v>19.896</v>
+        <v>19.112</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.13</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4</v>
+        <v>0.3602</v>
       </c>
       <c r="J64" t="n">
-        <v>16</v>
+        <v>14.408</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.1</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3254</v>
+        <v>0.2877</v>
       </c>
       <c r="J65" t="n">
-        <v>13.016</v>
+        <v>11.508</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.74</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7398</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.592</v>
+        <v>-28.448</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.25</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4962</v>
+        <v>0.4574</v>
       </c>
       <c r="J67" t="n">
-        <v>19.848</v>
+        <v>18.296</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0001</v>
+        <v>-0</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.004</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.98</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0428</v>
+        <v>-0.0325</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.712</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.9</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1471</v>
+        <v>-0.1275</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.884</v>
+        <v>-5.1</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.88</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.1695</v>
+        <v>-0.1492</v>
       </c>
       <c r="J71" t="n">
-        <v>-6.78</v>
+        <v>-5.968</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.54</v>
       </c>
       <c r="I72" t="n">
-        <v>0.9319</v>
+        <v>0.8869</v>
       </c>
       <c r="J72" t="n">
-        <v>27.957</v>
+        <v>26.607</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.22</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4531</v>
+        <v>0.3952</v>
       </c>
       <c r="J73" t="n">
-        <v>13.593</v>
+        <v>11.856</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.11</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2615</v>
+        <v>0.2157</v>
       </c>
       <c r="J74" t="n">
-        <v>7.845</v>
+        <v>6.471</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.75</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3067</v>
+        <v>-0.2896</v>
       </c>
       <c r="J75" t="n">
-        <v>-9.201000000000001</v>
+        <v>-8.688000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.71</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3441</v>
+        <v>-0.3296</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.323</v>
+        <v>-9.888</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.24</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6525</v>
+        <v>0.6167</v>
       </c>
       <c r="J77" t="n">
-        <v>19.575</v>
+        <v>18.501</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.15</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4486</v>
+        <v>0.4081</v>
       </c>
       <c r="J78" t="n">
-        <v>13.458</v>
+        <v>12.243</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.06</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2182</v>
+        <v>0.1864</v>
       </c>
       <c r="J79" t="n">
-        <v>6.546</v>
+        <v>5.592</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1238</v>
+        <v>0.1008</v>
       </c>
       <c r="J80" t="n">
-        <v>3.714</v>
+        <v>3.024</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.95</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2163</v>
+        <v>-0.1795</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.489</v>
+        <v>-5.385</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.11</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3014</v>
+        <v>0.2521</v>
       </c>
       <c r="J82" t="n">
-        <v>7.535</v>
+        <v>6.3025</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.89</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.149</v>
+        <v>-0.1316</v>
       </c>
       <c r="J83" t="n">
-        <v>-3.725</v>
+        <v>-3.29</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.84</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2009</v>
+        <v>-0.1817</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.0225</v>
+        <v>-4.5425</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.211</v>
+        <v>-0.1916</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.275</v>
+        <v>-4.79</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3174</v>
+        <v>-0.3002</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.935</v>
+        <v>-7.505</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.49</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0884</v>
+        <v>1.0986</v>
       </c>
       <c r="J87" t="n">
-        <v>27.21</v>
+        <v>27.465</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.31</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7712</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="J88" t="n">
-        <v>19.28</v>
+        <v>18.6375</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.27</v>
       </c>
       <c r="I89" t="n">
-        <v>0.6901</v>
+        <v>0.6604</v>
       </c>
       <c r="J89" t="n">
-        <v>17.2525</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.12</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3596</v>
+        <v>0.326</v>
       </c>
       <c r="J90" t="n">
-        <v>8.99</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.86</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4844</v>
+        <v>-0.4447</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.11</v>
+        <v>-11.1175</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.13</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3137</v>
+        <v>0.2621</v>
       </c>
       <c r="J92" t="n">
-        <v>13.1754</v>
+        <v>11.0082</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.151</v>
+        <v>0.1161</v>
       </c>
       <c r="J93" t="n">
-        <v>6.342</v>
+        <v>4.8762</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.03</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1027</v>
+        <v>0.0756</v>
       </c>
       <c r="J94" t="n">
-        <v>4.3134</v>
+        <v>3.1752</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.91</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1337</v>
+        <v>-0.1149</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.6154</v>
+        <v>-4.8258</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.78</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2702</v>
+        <v>-0.2509</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.3484</v>
+        <v>-10.5378</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.58</v>
       </c>
       <c r="I97" t="n">
-        <v>1.2391</v>
+        <v>1.2587</v>
       </c>
       <c r="J97" t="n">
-        <v>52.0422</v>
+        <v>52.8654</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.13</v>
       </c>
       <c r="I98" t="n">
-        <v>0.3976</v>
+        <v>0.3586</v>
       </c>
       <c r="J98" t="n">
-        <v>16.6992</v>
+        <v>15.0612</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.99</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0761</v>
+        <v>-0.0558</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.1962</v>
+        <v>-2.3436</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.92</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3079</v>
+        <v>-0.2666</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.9318</v>
+        <v>-11.1972</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.9</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3625</v>
+        <v>-0.32</v>
       </c>
       <c r="J101" t="n">
-        <v>-15.225</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.87</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9813</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>28.4577</v>
+        <v>26.7931</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2382</v>
+        <v>0.1927</v>
       </c>
       <c r="J103" t="n">
-        <v>6.9078</v>
+        <v>5.5883</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.03</v>
       </c>
       <c r="I104" t="n">
-        <v>0.0575</v>
+        <v>0.0407</v>
       </c>
       <c r="J104" t="n">
-        <v>1.6675</v>
+        <v>1.1803</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.98</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.0577</v>
+        <v>-0.0454</v>
       </c>
       <c r="J105" t="n">
-        <v>-1.6733</v>
+        <v>-1.3166</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.95</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.1017</v>
+        <v>-0.0848</v>
       </c>
       <c r="J106" t="n">
-        <v>-2.9493</v>
+        <v>-2.4592</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.21</v>
       </c>
       <c r="I107" t="n">
-        <v>0.3831</v>
+        <v>0.3823</v>
       </c>
       <c r="J107" t="n">
-        <v>11.1099</v>
+        <v>11.0867</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0895</v>
+        <v>-0.0759</v>
       </c>
       <c r="J108" t="n">
-        <v>-2.5955</v>
+        <v>-2.2011</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.8</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2403</v>
+        <v>-0.2209</v>
       </c>
       <c r="J109" t="n">
-        <v>-6.9687</v>
+        <v>-6.4061</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.73</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3074</v>
+        <v>-0.2898</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.9146</v>
+        <v>-8.404199999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3537</v>
+        <v>-0.3387</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.2573</v>
+        <v>-9.8223</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.16</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4406</v>
+        <v>0.3958</v>
       </c>
       <c r="J112" t="n">
-        <v>11.4556</v>
+        <v>10.2908</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.93</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.0876</v>
+        <v>-0.074</v>
       </c>
       <c r="J113" t="n">
-        <v>-2.2776</v>
+        <v>-1.924</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.71</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3151</v>
+        <v>-0.2991</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.192600000000001</v>
+        <v>-7.7766</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4674</v>
+        <v>-0.4624</v>
       </c>
       <c r="J115" t="n">
-        <v>-12.1524</v>
+        <v>-12.0224</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.51</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4936</v>
+        <v>-0.4917</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.8336</v>
+        <v>-12.7842</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.563</v>
+        <v>1.6033</v>
       </c>
       <c r="J117" t="n">
-        <v>40.638</v>
+        <v>41.6858</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.35</v>
       </c>
       <c r="I118" t="n">
-        <v>0.8442</v>
+        <v>0.8244</v>
       </c>
       <c r="J118" t="n">
-        <v>21.9492</v>
+        <v>21.4344</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.2</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5407</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>14.0582</v>
+        <v>13.2236</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.14</v>
       </c>
       <c r="I120" t="n">
-        <v>0.4035</v>
+        <v>0.3704</v>
       </c>
       <c r="J120" t="n">
-        <v>10.491</v>
+        <v>9.6304</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.66</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.9345</v>
+        <v>-0.9297</v>
       </c>
       <c r="J121" t="n">
-        <v>-24.297</v>
+        <v>-24.1722</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.2</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4938</v>
+        <v>0.4441</v>
       </c>
       <c r="J122" t="n">
-        <v>10.8636</v>
+        <v>9.770200000000001</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.82</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.2163</v>
+        <v>-0.1986</v>
       </c>
       <c r="J123" t="n">
-        <v>-4.7586</v>
+        <v>-4.3692</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.76</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.2733</v>
+        <v>-0.2554</v>
       </c>
       <c r="J124" t="n">
-        <v>-6.0126</v>
+        <v>-5.6188</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.73</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3015</v>
+        <v>-0.2842</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.633</v>
+        <v>-6.2524</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.57</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4462</v>
+        <v>-0.4391</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.8164</v>
+        <v>-9.6602</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.93</v>
       </c>
       <c r="I127" t="n">
-        <v>1.6114</v>
+        <v>1.6523</v>
       </c>
       <c r="J127" t="n">
-        <v>35.4508</v>
+        <v>36.3506</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.69</v>
       </c>
       <c r="I128" t="n">
-        <v>1.3176</v>
+        <v>1.3379</v>
       </c>
       <c r="J128" t="n">
-        <v>28.9872</v>
+        <v>29.4338</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6486</v>
+        <v>0.6251</v>
       </c>
       <c r="J129" t="n">
-        <v>14.2692</v>
+        <v>13.7522</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5369</v>
       </c>
       <c r="J130" t="n">
-        <v>12.408</v>
+        <v>11.8118</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.6298</v>
+        <v>-0.6016</v>
       </c>
       <c r="J131" t="n">
-        <v>-13.8556</v>
+        <v>-13.2352</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.08</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2292</v>
+        <v>0.1847</v>
       </c>
       <c r="J132" t="n">
-        <v>6.6468</v>
+        <v>5.3563</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.01</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0557</v>
+        <v>0.0379</v>
       </c>
       <c r="J133" t="n">
-        <v>1.6153</v>
+        <v>1.0991</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J134" t="n">
-        <v>-2.7202</v>
+        <v>-2.2939</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.83</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2146</v>
+        <v>-0.1946</v>
       </c>
       <c r="J135" t="n">
-        <v>-6.2234</v>
+        <v>-5.6434</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.73</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3121</v>
+        <v>-0.2946</v>
       </c>
       <c r="J136" t="n">
-        <v>-9.0509</v>
+        <v>-8.5434</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.48</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0778</v>
+        <v>1.087</v>
       </c>
       <c r="J137" t="n">
-        <v>31.2562</v>
+        <v>31.523</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.25</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6513</v>
+        <v>0.6194</v>
       </c>
       <c r="J138" t="n">
-        <v>18.8877</v>
+        <v>17.9626</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.15</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4344</v>
+        <v>0.3996</v>
       </c>
       <c r="J139" t="n">
-        <v>12.5976</v>
+        <v>11.5884</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.08</v>
       </c>
       <c r="I140" t="n">
-        <v>0.2577</v>
+        <v>0.2266</v>
       </c>
       <c r="J140" t="n">
-        <v>7.4733</v>
+        <v>6.5714</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>1.01</v>
       </c>
       <c r="I141" t="n">
-        <v>0.0273</v>
+        <v>0.0175</v>
       </c>
       <c r="J141" t="n">
-        <v>0.7917</v>
+        <v>0.5075</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.77</v>
       </c>
       <c r="I142" t="n">
-        <v>1.4249</v>
+        <v>1.4514</v>
       </c>
       <c r="J142" t="n">
-        <v>31.3478</v>
+        <v>31.9308</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.59</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1967</v>
+        <v>1.212</v>
       </c>
       <c r="J143" t="n">
-        <v>26.3274</v>
+        <v>26.664</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4811</v>
+        <v>0.4508</v>
       </c>
       <c r="J144" t="n">
-        <v>10.5842</v>
+        <v>9.9176</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2869</v>
+        <v>0.2553</v>
       </c>
       <c r="J145" t="n">
-        <v>6.3118</v>
+        <v>5.6166</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.08</v>
       </c>
       <c r="I146" t="n">
-        <v>0.2331</v>
+        <v>0.2026</v>
       </c>
       <c r="J146" t="n">
-        <v>5.1282</v>
+        <v>4.4572</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.09</v>
       </c>
       <c r="I147" t="n">
-        <v>0.317</v>
+        <v>0.2795</v>
       </c>
       <c r="J147" t="n">
-        <v>6.974</v>
+        <v>6.149</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.77</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2568</v>
+        <v>-0.2416</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.6496</v>
+        <v>-5.3152</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.75</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2756</v>
+        <v>-0.2604</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.0632</v>
+        <v>-5.7288</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3292</v>
+        <v>-0.3146</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.2424</v>
+        <v>-6.9212</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.36</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6188</v>
+        <v>-0.6353</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.6136</v>
+        <v>-13.9766</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.14</v>
       </c>
       <c r="I152" t="n">
-        <v>0.2837</v>
+        <v>0.2728</v>
       </c>
       <c r="J152" t="n">
-        <v>7.6599</v>
+        <v>7.3656</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.0892</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.4084</v>
+        <v>-2.0466</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.91</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1259</v>
+        <v>-0.11</v>
       </c>
       <c r="J154" t="n">
-        <v>-3.3993</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2302</v>
+        <v>-0.2109</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.2154</v>
+        <v>-5.6943</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4692</v>
+        <v>-0.4653</v>
       </c>
       <c r="J156" t="n">
-        <v>-12.6684</v>
+        <v>-12.5631</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.57</v>
       </c>
       <c r="I157" t="n">
-        <v>0.6903</v>
+        <v>0.6181</v>
       </c>
       <c r="J157" t="n">
-        <v>18.6381</v>
+        <v>16.6887</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.3</v>
       </c>
       <c r="I158" t="n">
-        <v>0.41</v>
+        <v>0.3481</v>
       </c>
       <c r="J158" t="n">
-        <v>11.07</v>
+        <v>9.3987</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.22</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3208</v>
+        <v>0.2668</v>
       </c>
       <c r="J159" t="n">
-        <v>8.6616</v>
+        <v>7.2036</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0726</v>
+        <v>0.0525</v>
       </c>
       <c r="J160" t="n">
-        <v>1.9602</v>
+        <v>1.4175</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.03</v>
       </c>
       <c r="I161" t="n">
-        <v>0.0541</v>
+        <v>0.0378</v>
       </c>
       <c r="J161" t="n">
-        <v>1.4607</v>
+        <v>1.0206</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.68</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3286</v>
+        <v>1.3496</v>
       </c>
       <c r="J162" t="n">
-        <v>37.2008</v>
+        <v>37.7888</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0636</v>
+        <v>1.0717</v>
       </c>
       <c r="J163" t="n">
-        <v>29.7808</v>
+        <v>30.0076</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3506</v>
+        <v>0.3182</v>
       </c>
       <c r="J164" t="n">
-        <v>9.816800000000001</v>
+        <v>8.909599999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.03</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0929</v>
+        <v>0.0723</v>
       </c>
       <c r="J165" t="n">
-        <v>2.6012</v>
+        <v>2.0244</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.02</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0564</v>
+        <v>0.04</v>
       </c>
       <c r="J166" t="n">
-        <v>1.5792</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.41</v>
       </c>
       <c r="I167" t="n">
-        <v>0.8012</v>
+        <v>0.7565</v>
       </c>
       <c r="J167" t="n">
-        <v>22.4336</v>
+        <v>21.182</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>0.0133</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J168" t="n">
-        <v>0.3724</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.84</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2035</v>
+        <v>-0.1836</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.698</v>
+        <v>-5.1408</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.78</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.2633</v>
+        <v>-0.2439</v>
       </c>
       <c r="J170" t="n">
-        <v>-7.3724</v>
+        <v>-6.8292</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.51</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.5072</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="J171" t="n">
-        <v>-14.2016</v>
+        <v>-14.2408</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.3</v>
       </c>
       <c r="I172" t="n">
-        <v>0.701</v>
+        <v>0.6696</v>
       </c>
       <c r="J172" t="n">
-        <v>14.721</v>
+        <v>14.0616</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>0.76</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.2684</v>
+        <v>-0.2523</v>
       </c>
       <c r="J173" t="n">
-        <v>-5.6364</v>
+        <v>-5.2983</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.74</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.2863</v>
+        <v>-0.2702</v>
       </c>
       <c r="J174" t="n">
-        <v>-6.0123</v>
+        <v>-5.6742</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3318</v>
+        <v>-0.3166</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.9678</v>
+        <v>-6.6486</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6801</v>
+        <v>-0.7089</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.2821</v>
+        <v>-14.8869</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>2.07</v>
       </c>
       <c r="I177" t="n">
-        <v>1.7583</v>
+        <v>1.8123</v>
       </c>
       <c r="J177" t="n">
-        <v>36.9243</v>
+        <v>38.0583</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.83</v>
       </c>
       <c r="I178" t="n">
-        <v>1.4757</v>
+        <v>1.5055</v>
       </c>
       <c r="J178" t="n">
-        <v>30.9897</v>
+        <v>31.6155</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>1.45</v>
       </c>
       <c r="I179" t="n">
-        <v>0.995</v>
+        <v>1.0004</v>
       </c>
       <c r="J179" t="n">
-        <v>20.895</v>
+        <v>21.0084</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>1.29</v>
       </c>
       <c r="I180" t="n">
-        <v>0.6992</v>
+        <v>0.6802</v>
       </c>
       <c r="J180" t="n">
-        <v>14.6832</v>
+        <v>14.2842</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.65</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.9811</v>
+        <v>-0.9883999999999999</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.6031</v>
+        <v>-20.7564</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>2.09</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7763</v>
+        <v>1.8318</v>
       </c>
       <c r="J182" t="n">
-        <v>35.526</v>
+        <v>36.636</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.97</v>
       </c>
       <c r="I183" t="n">
-        <v>1.6374</v>
+        <v>1.6795</v>
       </c>
       <c r="J183" t="n">
-        <v>32.748</v>
+        <v>33.59</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.2</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5059</v>
+        <v>0.4772</v>
       </c>
       <c r="J184" t="n">
-        <v>10.118</v>
+        <v>9.544</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.11</v>
       </c>
       <c r="I185" t="n">
-        <v>0.2925</v>
+        <v>0.259</v>
       </c>
       <c r="J185" t="n">
-        <v>5.85</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.03</v>
       </c>
       <c r="I186" t="n">
-        <v>0.0601</v>
+        <v>0.0356</v>
       </c>
       <c r="J186" t="n">
-        <v>1.202</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.04</v>
       </c>
       <c r="I187" t="n">
-        <v>0.1979</v>
+        <v>0.1685</v>
       </c>
       <c r="J187" t="n">
-        <v>3.958</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.85</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.1757</v>
+        <v>-0.1601</v>
       </c>
       <c r="J188" t="n">
-        <v>-3.514</v>
+        <v>-3.202</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.76</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2667</v>
+        <v>-0.2514</v>
       </c>
       <c r="J189" t="n">
-        <v>-5.334</v>
+        <v>-5.028</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.64</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3746</v>
+        <v>-0.3617</v>
       </c>
       <c r="J190" t="n">
-        <v>-7.492</v>
+        <v>-7.234</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.39</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5935</v>
+        <v>-0.6057</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.87</v>
+        <v>-12.114</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.33</v>
       </c>
       <c r="I192" t="n">
-        <v>0.6322</v>
+        <v>0.573</v>
       </c>
       <c r="J192" t="n">
-        <v>14.5406</v>
+        <v>13.179</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.24</v>
       </c>
       <c r="I193" t="n">
-        <v>0.4903</v>
+        <v>0.4313</v>
       </c>
       <c r="J193" t="n">
-        <v>11.2769</v>
+        <v>9.9199</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.11</v>
       </c>
       <c r="I194" t="n">
-        <v>0.2645</v>
+        <v>0.2178</v>
       </c>
       <c r="J194" t="n">
-        <v>6.0835</v>
+        <v>5.0094</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0026</v>
+        <v>-0.0015</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.0598</v>
+        <v>-0.0345</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.54</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.4923</v>
+        <v>-0.4935</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.3229</v>
+        <v>-11.3505</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.34</v>
       </c>
       <c r="I197" t="n">
-        <v>0.8297</v>
+        <v>0.8078</v>
       </c>
       <c r="J197" t="n">
-        <v>19.0831</v>
+        <v>18.5794</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.31</v>
       </c>
       <c r="I198" t="n">
-        <v>0.7701</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="J198" t="n">
-        <v>17.7123</v>
+        <v>17.1235</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.22</v>
       </c>
       <c r="I199" t="n">
-        <v>0.5859</v>
+        <v>0.5533</v>
       </c>
       <c r="J199" t="n">
-        <v>13.4757</v>
+        <v>12.7259</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.12</v>
       </c>
       <c r="I200" t="n">
-        <v>0.3586</v>
+        <v>0.3253</v>
       </c>
       <c r="J200" t="n">
-        <v>8.2478</v>
+        <v>7.4819</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.09</v>
       </c>
       <c r="I201" t="n">
-        <v>0.2812</v>
+        <v>0.2495</v>
       </c>
       <c r="J201" t="n">
-        <v>6.4676</v>
+        <v>5.7385</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.27</v>
       </c>
       <c r="I202" t="n">
-        <v>0.7269</v>
+        <v>0.695</v>
       </c>
       <c r="J202" t="n">
-        <v>30.5298</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.19</v>
       </c>
       <c r="I203" t="n">
-        <v>0.5495</v>
+        <v>0.5092</v>
       </c>
       <c r="J203" t="n">
-        <v>23.079</v>
+        <v>21.3864</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.03</v>
       </c>
       <c r="I204" t="n">
-        <v>0.129</v>
+        <v>0.1043</v>
       </c>
       <c r="J204" t="n">
-        <v>5.418</v>
+        <v>4.3806</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.2099</v>
+        <v>-0.1737</v>
       </c>
       <c r="J205" t="n">
-        <v>-8.815799999999999</v>
+        <v>-7.2954</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.82</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.5515</v>
+        <v>-0.5111</v>
       </c>
       <c r="J206" t="n">
-        <v>-23.163</v>
+        <v>-21.4662</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.22</v>
       </c>
       <c r="I207" t="n">
-        <v>0.4605</v>
+        <v>0.4022</v>
       </c>
       <c r="J207" t="n">
-        <v>19.341</v>
+        <v>16.8924</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.09</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2279</v>
+        <v>0.1845</v>
       </c>
       <c r="J208" t="n">
-        <v>9.5718</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.01</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0409</v>
+        <v>0.0283</v>
       </c>
       <c r="J209" t="n">
-        <v>1.7178</v>
+        <v>1.1886</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.99</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.0271</v>
+        <v>-0.0193</v>
       </c>
       <c r="J210" t="n">
-        <v>-1.1382</v>
+        <v>-0.8106</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.84</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2146</v>
+        <v>-0.194</v>
       </c>
       <c r="J211" t="n">
-        <v>-9.013199999999999</v>
+        <v>-8.148</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.15</v>
       </c>
       <c r="I212" t="n">
-        <v>0.4112</v>
+        <v>0.3639</v>
       </c>
       <c r="J212" t="n">
-        <v>8.635199999999999</v>
+        <v>7.6419</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.04</v>
       </c>
       <c r="I213" t="n">
-        <v>0.1752</v>
+        <v>0.1422</v>
       </c>
       <c r="J213" t="n">
-        <v>3.6792</v>
+        <v>2.9862</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.6</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.417</v>
+        <v>-0.4069</v>
       </c>
       <c r="J214" t="n">
-        <v>-8.757</v>
+        <v>-8.5449</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.59</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.4259</v>
+        <v>-0.4166</v>
       </c>
       <c r="J215" t="n">
-        <v>-8.943899999999999</v>
+        <v>-8.7486</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.58</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4347</v>
+        <v>-0.4263</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.1287</v>
+        <v>-8.952299999999999</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.82</v>
       </c>
       <c r="I217" t="n">
-        <v>1.4895</v>
+        <v>1.5208</v>
       </c>
       <c r="J217" t="n">
-        <v>31.2795</v>
+        <v>31.9368</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.45</v>
       </c>
       <c r="I218" t="n">
-        <v>1.0084</v>
+        <v>1.0103</v>
       </c>
       <c r="J218" t="n">
-        <v>21.1764</v>
+        <v>21.2163</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.28</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6962</v>
+        <v>0.6731</v>
       </c>
       <c r="J219" t="n">
-        <v>14.6202</v>
+        <v>14.1351</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.2</v>
       </c>
       <c r="I220" t="n">
-        <v>0.5278</v>
+        <v>0.4984</v>
       </c>
       <c r="J220" t="n">
-        <v>11.0838</v>
+        <v>10.4664</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.91</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3748</v>
+        <v>-0.3375</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.8708</v>
+        <v>-7.0875</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.31</v>
       </c>
       <c r="I222" t="n">
-        <v>0.5994</v>
+        <v>0.5397</v>
       </c>
       <c r="J222" t="n">
-        <v>16.7832</v>
+        <v>15.1116</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2633</v>
+        <v>0.217</v>
       </c>
       <c r="J223" t="n">
-        <v>7.3724</v>
+        <v>6.076</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.99</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.0287</v>
+        <v>-0.0204</v>
       </c>
       <c r="J224" t="n">
-        <v>-0.8036</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.98</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.0464</v>
+        <v>-0.035</v>
       </c>
       <c r="J225" t="n">
-        <v>-1.2992</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.87</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.1847</v>
+        <v>-0.1641</v>
       </c>
       <c r="J226" t="n">
-        <v>-5.1716</v>
+        <v>-4.5948</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.27</v>
       </c>
       <c r="I227" t="n">
-        <v>0.7257</v>
+        <v>0.6937</v>
       </c>
       <c r="J227" t="n">
-        <v>20.3196</v>
+        <v>19.4236</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.25</v>
       </c>
       <c r="I228" t="n">
-        <v>0.6824</v>
+        <v>0.6478</v>
       </c>
       <c r="J228" t="n">
-        <v>19.1072</v>
+        <v>18.1384</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.05</v>
       </c>
       <c r="I229" t="n">
-        <v>0.1924</v>
+        <v>0.1612</v>
       </c>
       <c r="J229" t="n">
-        <v>5.3872</v>
+        <v>4.5136</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1788</v>
+        <v>-0.1452</v>
       </c>
       <c r="J230" t="n">
-        <v>-5.0064</v>
+        <v>-4.0656</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.75</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7117</v>
+        <v>-0.6803</v>
       </c>
       <c r="J231" t="n">
-        <v>-19.9276</v>
+        <v>-19.0484</v>
       </c>
     </row>
   </sheetData>
